--- a/research/traditional_assets/database/data/romania/romania_green_renewable_energy.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_green_renewable_energy.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08779238589248206</v>
+        <v>0.08768971807505409</v>
       </c>
       <c r="C2">
-        <v>11516.88193981801</v>
+        <v>11413.80685383577</v>
       </c>
       <c r="D2">
-        <v>11397.18193981801</v>
+        <v>11409.19385383577</v>
       </c>
       <c r="E2">
-        <v>-86.90000000000001</v>
+        <v>28.18699999999998</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>115.087</v>
       </c>
       <c r="G2">
         <v>119.7</v>
@@ -1439,28 +1439,28 @@
         <v>1191.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>5.7888761</v>
       </c>
       <c r="N2">
-        <v>1191.1</v>
+        <v>1185.3111239</v>
       </c>
       <c r="O2">
-        <v>190.576</v>
+        <v>189.649779824</v>
       </c>
       <c r="P2">
-        <v>1000.524</v>
+        <v>995.661344076</v>
       </c>
       <c r="Q2">
-        <v>1196.424</v>
+        <v>1191.561344076</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08779238589248206</v>
+        <v>0.08814868492429706</v>
       </c>
       <c r="T2">
-        <v>0.5780409979533054</v>
+        <v>0.5829455882389699</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>205.7566925642095</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08768971807505409</v>
+        <v>0.08758705025762611</v>
       </c>
       <c r="C3">
-        <v>11413.80685383577</v>
+        <v>11310.75711417301</v>
       </c>
       <c r="D3">
-        <v>11409.19385383577</v>
+        <v>11421.23111417301</v>
       </c>
       <c r="E3">
-        <v>28.18699999999998</v>
+        <v>143.274</v>
       </c>
       <c r="F3">
-        <v>115.087</v>
+        <v>230.174</v>
       </c>
       <c r="G3">
         <v>119.7</v>
@@ -1521,28 +1521,28 @@
         <v>1191.1</v>
       </c>
       <c r="M3">
-        <v>5.7888761</v>
+        <v>11.5777522</v>
       </c>
       <c r="N3">
-        <v>1185.3111239</v>
+        <v>1179.5222478</v>
       </c>
       <c r="O3">
-        <v>189.649779824</v>
+        <v>188.723559648</v>
       </c>
       <c r="P3">
-        <v>995.661344076</v>
+        <v>990.7986881519998</v>
       </c>
       <c r="Q3">
-        <v>1191.561344076</v>
+        <v>1186.698688152</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08814868492429706</v>
+        <v>0.0885122553649246</v>
       </c>
       <c r="T3">
-        <v>0.5829455882389699</v>
+        <v>0.5879502722039335</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>205.7566925642095</v>
+        <v>102.8783462821047</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08758705025762611</v>
+        <v>0.08748438244019814</v>
       </c>
       <c r="C4">
-        <v>11310.75711417301</v>
+        <v>11207.7328011393</v>
       </c>
       <c r="D4">
-        <v>11421.23111417301</v>
+        <v>11433.2938011393</v>
       </c>
       <c r="E4">
-        <v>143.274</v>
+        <v>258.361</v>
       </c>
       <c r="F4">
-        <v>230.174</v>
+        <v>345.261</v>
       </c>
       <c r="G4">
         <v>119.7</v>
@@ -1603,28 +1603,28 @@
         <v>1191.1</v>
       </c>
       <c r="M4">
-        <v>11.5777522</v>
+        <v>17.3666283</v>
       </c>
       <c r="N4">
-        <v>1179.5222478</v>
+        <v>1173.7333717</v>
       </c>
       <c r="O4">
-        <v>188.723559648</v>
+        <v>187.797339472</v>
       </c>
       <c r="P4">
-        <v>990.7986881519998</v>
+        <v>985.9360322279999</v>
       </c>
       <c r="Q4">
-        <v>1186.698688152</v>
+        <v>1181.836032228</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0885122553649246</v>
+        <v>0.08888332210329705</v>
       </c>
       <c r="T4">
-        <v>0.5879502722039335</v>
+        <v>0.5930581455289995</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>102.8783462821047</v>
+        <v>68.58556418806982</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08748438244019814</v>
+        <v>0.08738171462277017</v>
       </c>
       <c r="C5">
-        <v>11207.7328011393</v>
+        <v>11104.73399538383</v>
       </c>
       <c r="D5">
-        <v>11433.2938011393</v>
+        <v>11445.38199538383</v>
       </c>
       <c r="E5">
-        <v>258.361</v>
+        <v>373.448</v>
       </c>
       <c r="F5">
-        <v>345.261</v>
+        <v>460.348</v>
       </c>
       <c r="G5">
         <v>119.7</v>
@@ -1685,28 +1685,28 @@
         <v>1191.1</v>
       </c>
       <c r="M5">
-        <v>17.3666283</v>
+        <v>23.1555044</v>
       </c>
       <c r="N5">
-        <v>1173.7333717</v>
+        <v>1167.9444956</v>
       </c>
       <c r="O5">
-        <v>187.797339472</v>
+        <v>186.871119296</v>
       </c>
       <c r="P5">
-        <v>985.9360322279999</v>
+        <v>981.073376304</v>
       </c>
       <c r="Q5">
-        <v>1181.836032228</v>
+        <v>1176.973376304</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08888332210329705</v>
+        <v>0.08926211939871893</v>
       </c>
       <c r="T5">
-        <v>0.5930581455289995</v>
+        <v>0.5982724328816711</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>68.58556418806982</v>
+        <v>51.43917314105237</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08738171462277017</v>
+        <v>0.08727904680534221</v>
       </c>
       <c r="C6">
-        <v>11104.73399538383</v>
+        <v>11001.76077789726</v>
       </c>
       <c r="D6">
-        <v>11445.38199538383</v>
+        <v>11457.49577789726</v>
       </c>
       <c r="E6">
-        <v>373.448</v>
+        <v>488.535</v>
       </c>
       <c r="F6">
-        <v>460.348</v>
+        <v>575.4349999999999</v>
       </c>
       <c r="G6">
         <v>119.7</v>
@@ -1767,28 +1767,28 @@
         <v>1191.1</v>
       </c>
       <c r="M6">
-        <v>23.1555044</v>
+        <v>28.94438049999999</v>
       </c>
       <c r="N6">
-        <v>1167.9444956</v>
+        <v>1162.1556195</v>
       </c>
       <c r="O6">
-        <v>186.871119296</v>
+        <v>185.94489912</v>
       </c>
       <c r="P6">
-        <v>981.073376304</v>
+        <v>976.2107203799999</v>
       </c>
       <c r="Q6">
-        <v>1176.973376304</v>
+        <v>1172.11072038</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08926211939871893</v>
+        <v>0.08964889137404443</v>
       </c>
       <c r="T6">
-        <v>0.5982724328816711</v>
+        <v>0.6035964947049253</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>51.43917314105237</v>
+        <v>41.1513385128419</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08727904680534221</v>
+        <v>0.08717637898791424</v>
       </c>
       <c r="C7">
-        <v>11001.76077789726</v>
+        <v>10898.81323001347</v>
       </c>
       <c r="D7">
-        <v>11457.49577789726</v>
+        <v>11469.63523001347</v>
       </c>
       <c r="E7">
-        <v>488.535</v>
+        <v>603.622</v>
       </c>
       <c r="F7">
-        <v>575.4349999999999</v>
+        <v>690.5219999999999</v>
       </c>
       <c r="G7">
         <v>119.7</v>
@@ -1849,28 +1849,28 @@
         <v>1191.1</v>
       </c>
       <c r="M7">
-        <v>28.94438049999999</v>
+        <v>34.7332566</v>
       </c>
       <c r="N7">
-        <v>1162.1556195</v>
+        <v>1156.3667434</v>
       </c>
       <c r="O7">
-        <v>185.94489912</v>
+        <v>185.018678944</v>
       </c>
       <c r="P7">
-        <v>976.2107203799999</v>
+        <v>971.348064456</v>
       </c>
       <c r="Q7">
-        <v>1172.11072038</v>
+        <v>1167.248064456</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08964889137404443</v>
+        <v>0.09004389254033429</v>
       </c>
       <c r="T7">
-        <v>0.6035964947049253</v>
+        <v>0.6090338344393125</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>41.1513385128419</v>
+        <v>34.29278209403491</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08717637898791424</v>
+        <v>0.08707371117048626</v>
       </c>
       <c r="C8">
-        <v>10898.81323001347</v>
+        <v>10795.89143341143</v>
       </c>
       <c r="D8">
-        <v>11469.63523001347</v>
+        <v>11481.80043341143</v>
       </c>
       <c r="E8">
-        <v>603.622</v>
+        <v>718.7089999999998</v>
       </c>
       <c r="F8">
-        <v>690.5219999999999</v>
+        <v>805.6089999999998</v>
       </c>
       <c r="G8">
         <v>119.7</v>
@@ -1931,28 +1931,28 @@
         <v>1191.1</v>
       </c>
       <c r="M8">
-        <v>34.7332566</v>
+        <v>40.52213269999999</v>
       </c>
       <c r="N8">
-        <v>1156.3667434</v>
+        <v>1150.5778673</v>
       </c>
       <c r="O8">
-        <v>185.018678944</v>
+        <v>184.092458768</v>
       </c>
       <c r="P8">
-        <v>971.348064456</v>
+        <v>966.485408532</v>
       </c>
       <c r="Q8">
-        <v>1167.248064456</v>
+        <v>1162.385408532</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09004389254033429</v>
+        <v>0.09044738835536158</v>
       </c>
       <c r="T8">
-        <v>0.6090338344393125</v>
+        <v>0.6145881062109984</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>34.29278209403491</v>
+        <v>29.39381322345851</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08707371117048626</v>
+        <v>0.0869710433530583</v>
       </c>
       <c r="C9">
-        <v>10795.89143341143</v>
+        <v>10692.99547011698</v>
       </c>
       <c r="D9">
-        <v>11481.80043341143</v>
+        <v>11493.99147011698</v>
       </c>
       <c r="E9">
-        <v>718.7090000000001</v>
+        <v>833.7959999999999</v>
       </c>
       <c r="F9">
-        <v>805.609</v>
+        <v>920.6959999999999</v>
       </c>
       <c r="G9">
         <v>119.7</v>
@@ -2013,28 +2013,28 @@
         <v>1191.1</v>
       </c>
       <c r="M9">
-        <v>40.5221327</v>
+        <v>46.3110088</v>
       </c>
       <c r="N9">
-        <v>1150.5778673</v>
+        <v>1144.7889912</v>
       </c>
       <c r="O9">
-        <v>184.092458768</v>
+        <v>183.166238592</v>
       </c>
       <c r="P9">
-        <v>966.485408532</v>
+        <v>961.6227526079998</v>
       </c>
       <c r="Q9">
-        <v>1162.385408532</v>
+        <v>1157.522752608</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09044738835536158</v>
+        <v>0.09085965581854162</v>
       </c>
       <c r="T9">
-        <v>0.6145881062109984</v>
+        <v>0.620263123021199</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>29.3938132234585</v>
+        <v>25.71958657052618</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0869710433530583</v>
+        <v>0.08686837553563032</v>
       </c>
       <c r="C10">
-        <v>10692.99547011698</v>
+        <v>10590.12542250471</v>
       </c>
       <c r="D10">
-        <v>11493.99147011698</v>
+        <v>11506.20842250471</v>
       </c>
       <c r="E10">
-        <v>833.7959999999999</v>
+        <v>948.8829999999999</v>
       </c>
       <c r="F10">
-        <v>920.6959999999999</v>
+        <v>1035.783</v>
       </c>
       <c r="G10">
         <v>119.7</v>
@@ -2095,28 +2095,28 @@
         <v>1191.1</v>
       </c>
       <c r="M10">
-        <v>46.3110088</v>
+        <v>52.09988489999999</v>
       </c>
       <c r="N10">
-        <v>1144.7889912</v>
+        <v>1139.0001151</v>
       </c>
       <c r="O10">
-        <v>183.166238592</v>
+        <v>182.240018416</v>
       </c>
       <c r="P10">
-        <v>961.6227526079998</v>
+        <v>956.7600966839999</v>
       </c>
       <c r="Q10">
-        <v>1157.522752608</v>
+        <v>1152.660096684</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09085965581854162</v>
+        <v>0.09128098410508825</v>
       </c>
       <c r="T10">
-        <v>0.620263123021199</v>
+        <v>0.62606286547558</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>25.71958657052618</v>
+        <v>22.86185472935661</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08686837553563032</v>
+        <v>0.08676570771820236</v>
       </c>
       <c r="C11">
-        <v>10590.12542250471</v>
+        <v>10487.28137329982</v>
       </c>
       <c r="D11">
-        <v>11506.20842250471</v>
+        <v>11518.45137329982</v>
       </c>
       <c r="E11">
-        <v>948.8829999999999</v>
+        <v>1063.97</v>
       </c>
       <c r="F11">
-        <v>1035.783</v>
+        <v>1150.87</v>
       </c>
       <c r="G11">
         <v>119.7</v>
@@ -2177,28 +2177,28 @@
         <v>1191.1</v>
       </c>
       <c r="M11">
-        <v>52.09988489999999</v>
+        <v>57.88876099999999</v>
       </c>
       <c r="N11">
-        <v>1139.0001151</v>
+        <v>1133.211239</v>
       </c>
       <c r="O11">
-        <v>182.240018416</v>
+        <v>181.31379824</v>
       </c>
       <c r="P11">
-        <v>956.7600966839999</v>
+        <v>951.89744076</v>
       </c>
       <c r="Q11">
-        <v>1152.660096684</v>
+        <v>1147.79744076</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09128098410508825</v>
+        <v>0.09171167524244705</v>
       </c>
       <c r="T11">
-        <v>0.62606286547558</v>
+        <v>0.6319914910956139</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.86185472935661</v>
+        <v>20.57566925642095</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08676570771820236</v>
+        <v>0.08666303990077437</v>
       </c>
       <c r="C12">
-        <v>10487.28137329982</v>
+        <v>10384.46340557995</v>
       </c>
       <c r="D12">
-        <v>11518.45137329982</v>
+        <v>11530.72040557995</v>
       </c>
       <c r="E12">
-        <v>1063.97</v>
+        <v>1179.057</v>
       </c>
       <c r="F12">
-        <v>1150.87</v>
+        <v>1265.957</v>
       </c>
       <c r="G12">
         <v>119.7</v>
@@ -2259,28 +2259,28 @@
         <v>1191.1</v>
       </c>
       <c r="M12">
-        <v>57.88876099999999</v>
+        <v>63.67763709999999</v>
       </c>
       <c r="N12">
-        <v>1133.211239</v>
+        <v>1127.4223629</v>
       </c>
       <c r="O12">
-        <v>181.31379824</v>
+        <v>180.387578064</v>
       </c>
       <c r="P12">
-        <v>951.89744076</v>
+        <v>947.0347848359999</v>
       </c>
       <c r="Q12">
-        <v>1147.79744076</v>
+        <v>1142.934784836</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09171167524244705</v>
+        <v>0.09215204483233076</v>
       </c>
       <c r="T12">
-        <v>0.6319914910956139</v>
+        <v>0.6380533442576711</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.57566925642095</v>
+        <v>18.70515386947359</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08666303990077437</v>
+        <v>0.08656037208334641</v>
       </c>
       <c r="C13">
-        <v>10384.46340557995</v>
+        <v>10281.6716027771</v>
       </c>
       <c r="D13">
-        <v>11530.72040557995</v>
+        <v>11543.0156027771</v>
       </c>
       <c r="E13">
-        <v>1179.057</v>
+        <v>1294.144</v>
       </c>
       <c r="F13">
-        <v>1265.957</v>
+        <v>1381.044</v>
       </c>
       <c r="G13">
         <v>119.7</v>
@@ -2341,28 +2341,28 @@
         <v>1191.1</v>
       </c>
       <c r="M13">
-        <v>63.67763709999999</v>
+        <v>69.46651319999999</v>
       </c>
       <c r="N13">
-        <v>1127.4223629</v>
+        <v>1121.6334868</v>
       </c>
       <c r="O13">
-        <v>180.387578064</v>
+        <v>179.461357888</v>
       </c>
       <c r="P13">
-        <v>947.0347848359999</v>
+        <v>942.1721289119999</v>
       </c>
       <c r="Q13">
-        <v>1142.934784836</v>
+        <v>1138.072128912</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09215204483233076</v>
+        <v>0.09260242282198455</v>
       </c>
       <c r="T13">
-        <v>0.6380533442576711</v>
+        <v>0.644252966809775</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.70515386947359</v>
+        <v>17.14639104701746</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08656037208334641</v>
+        <v>0.08645770426591844</v>
       </c>
       <c r="C14">
-        <v>10281.6716027771</v>
+        <v>10178.90604867951</v>
       </c>
       <c r="D14">
-        <v>11543.0156027771</v>
+        <v>11555.33704867951</v>
       </c>
       <c r="E14">
-        <v>1294.144</v>
+        <v>1409.231</v>
       </c>
       <c r="F14">
-        <v>1381.044</v>
+        <v>1496.131</v>
       </c>
       <c r="G14">
         <v>119.7</v>
@@ -2423,28 +2423,28 @@
         <v>1191.1</v>
       </c>
       <c r="M14">
-        <v>69.46651319999999</v>
+        <v>75.25538929999999</v>
       </c>
       <c r="N14">
-        <v>1121.6334868</v>
+        <v>1115.8446107</v>
       </c>
       <c r="O14">
-        <v>179.461357888</v>
+        <v>178.535137712</v>
       </c>
       <c r="P14">
-        <v>942.1721289119999</v>
+        <v>937.3094729879999</v>
       </c>
       <c r="Q14">
-        <v>1138.072128912</v>
+        <v>1133.209472988</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09260242282198455</v>
+        <v>0.09306315432864189</v>
       </c>
       <c r="T14">
-        <v>0.644252966809775</v>
+        <v>0.650595109420548</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.14639104701746</v>
+        <v>15.82743788955458</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08645770426591844</v>
+        <v>0.08635503644849045</v>
       </c>
       <c r="C15">
-        <v>10178.90604867951</v>
+        <v>10076.16682743353</v>
       </c>
       <c r="D15">
-        <v>11555.33704867951</v>
+        <v>11567.68482743353</v>
       </c>
       <c r="E15">
-        <v>1409.231</v>
+        <v>1524.318</v>
       </c>
       <c r="F15">
-        <v>1496.131</v>
+        <v>1611.218</v>
       </c>
       <c r="G15">
         <v>119.7</v>
@@ -2505,28 +2505,28 @@
         <v>1191.1</v>
       </c>
       <c r="M15">
-        <v>75.25538929999999</v>
+        <v>81.0442654</v>
       </c>
       <c r="N15">
-        <v>1115.8446107</v>
+        <v>1110.0557346</v>
       </c>
       <c r="O15">
-        <v>178.535137712</v>
+        <v>177.608917536</v>
       </c>
       <c r="P15">
-        <v>937.3094729879999</v>
+        <v>932.4468170639998</v>
       </c>
       <c r="Q15">
-        <v>1133.209472988</v>
+        <v>1128.346817064</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09306315432864189</v>
+        <v>0.09353460052150053</v>
       </c>
       <c r="T15">
-        <v>0.650595109420548</v>
+        <v>0.6570847437199435</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.82743788955458</v>
+        <v>14.69690661172925</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08635503644849045</v>
+        <v>0.08625236863106249</v>
       </c>
       <c r="C16">
-        <v>10076.16682743353</v>
+        <v>9973.454023545581</v>
       </c>
       <c r="D16">
-        <v>11567.68482743353</v>
+        <v>11580.05902354558</v>
       </c>
       <c r="E16">
-        <v>1524.318</v>
+        <v>1639.405</v>
       </c>
       <c r="F16">
-        <v>1611.218</v>
+        <v>1726.305</v>
       </c>
       <c r="G16">
         <v>119.7</v>
@@ -2587,28 +2587,28 @@
         <v>1191.1</v>
       </c>
       <c r="M16">
-        <v>81.0442654</v>
+        <v>86.8331415</v>
       </c>
       <c r="N16">
-        <v>1110.0557346</v>
+        <v>1104.2668585</v>
       </c>
       <c r="O16">
-        <v>177.608917536</v>
+        <v>176.68269736</v>
       </c>
       <c r="P16">
-        <v>932.4468170639998</v>
+        <v>927.5841611399999</v>
       </c>
       <c r="Q16">
-        <v>1128.346817064</v>
+        <v>1123.48416114</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09353460052150053</v>
+        <v>0.09401713956595587</v>
       </c>
       <c r="T16">
-        <v>0.6570847437199435</v>
+        <v>0.6637270752969718</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.69690661172925</v>
+        <v>13.71711283761396</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08625236863106249</v>
+        <v>0.08614970081363452</v>
       </c>
       <c r="C17">
-        <v>9973.454023545581</v>
+        <v>9870.767721884064</v>
       </c>
       <c r="D17">
-        <v>11580.05902354558</v>
+        <v>11592.45972188406</v>
       </c>
       <c r="E17">
-        <v>1639.405</v>
+        <v>1754.492</v>
       </c>
       <c r="F17">
-        <v>1726.305</v>
+        <v>1841.392</v>
       </c>
       <c r="G17">
         <v>119.7</v>
@@ -2669,28 +2669,28 @@
         <v>1191.1</v>
       </c>
       <c r="M17">
-        <v>86.83314149999998</v>
+        <v>92.62201759999999</v>
       </c>
       <c r="N17">
-        <v>1104.2668585</v>
+        <v>1098.4779824</v>
       </c>
       <c r="O17">
-        <v>176.68269736</v>
+        <v>175.756477184</v>
       </c>
       <c r="P17">
-        <v>927.5841611399999</v>
+        <v>922.721505216</v>
       </c>
       <c r="Q17">
-        <v>1123.48416114</v>
+        <v>1118.621505216</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09401713956595587</v>
+        <v>0.0945111676352792</v>
       </c>
       <c r="T17">
-        <v>0.6637270752969718</v>
+        <v>0.6705275576258343</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>13.71711283761397</v>
+        <v>12.85979328526309</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08614970081363452</v>
+        <v>0.08604703299620654</v>
       </c>
       <c r="C18">
-        <v>9870.767721884064</v>
+        <v>9768.108007681298</v>
       </c>
       <c r="D18">
-        <v>11592.45972188406</v>
+        <v>11604.8870076813</v>
       </c>
       <c r="E18">
-        <v>1754.492</v>
+        <v>1869.579</v>
       </c>
       <c r="F18">
-        <v>1841.392</v>
+        <v>1956.479</v>
       </c>
       <c r="G18">
         <v>119.7</v>
@@ -2751,28 +2751,28 @@
         <v>1191.1</v>
       </c>
       <c r="M18">
-        <v>92.62201759999999</v>
+        <v>98.4108937</v>
       </c>
       <c r="N18">
-        <v>1098.4779824</v>
+        <v>1092.6891063</v>
       </c>
       <c r="O18">
-        <v>175.756477184</v>
+        <v>174.830257008</v>
       </c>
       <c r="P18">
-        <v>922.721505216</v>
+        <v>917.8588492919998</v>
       </c>
       <c r="Q18">
-        <v>1118.621505216</v>
+        <v>1113.758849292</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0945111676352792</v>
+        <v>0.09501709999542958</v>
       </c>
       <c r="T18">
-        <v>0.6705275576258343</v>
+        <v>0.6774919069987657</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.85979328526309</v>
+        <v>12.1033348567182</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08604703299620654</v>
+        <v>0.08594436517877858</v>
       </c>
       <c r="C19">
-        <v>9768.108007681298</v>
+        <v>9665.474966535474</v>
       </c>
       <c r="D19">
-        <v>11604.8870076813</v>
+        <v>11617.34096653547</v>
       </c>
       <c r="E19">
-        <v>1869.579</v>
+        <v>1984.666</v>
       </c>
       <c r="F19">
-        <v>1956.479</v>
+        <v>2071.566</v>
       </c>
       <c r="G19">
         <v>119.7</v>
@@ -2833,28 +2833,28 @@
         <v>1191.1</v>
       </c>
       <c r="M19">
-        <v>98.4108937</v>
+        <v>104.1997698</v>
       </c>
       <c r="N19">
-        <v>1092.6891063</v>
+        <v>1086.9002302</v>
       </c>
       <c r="O19">
-        <v>174.830257008</v>
+        <v>173.904036832</v>
       </c>
       <c r="P19">
-        <v>917.8588492919998</v>
+        <v>912.9961933679999</v>
       </c>
       <c r="Q19">
-        <v>1113.758849292</v>
+        <v>1108.896193368</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09501709999542958</v>
+        <v>0.09553537216924217</v>
       </c>
       <c r="T19">
-        <v>0.6774919069987657</v>
+        <v>0.6846261185515247</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>12.1033348567182</v>
+        <v>11.4309273646783</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08594436517877858</v>
+        <v>0.08584169736135061</v>
       </c>
       <c r="C20">
-        <v>9665.474966535476</v>
+        <v>9562.868684412628</v>
       </c>
       <c r="D20">
-        <v>11617.34096653547</v>
+        <v>11629.82168441263</v>
       </c>
       <c r="E20">
-        <v>1984.666</v>
+        <v>2099.753</v>
       </c>
       <c r="F20">
-        <v>2071.566</v>
+        <v>2186.653</v>
       </c>
       <c r="G20">
         <v>119.7</v>
@@ -2915,28 +2915,28 @@
         <v>1191.1</v>
       </c>
       <c r="M20">
-        <v>104.1997698</v>
+        <v>109.9886459</v>
       </c>
       <c r="N20">
-        <v>1086.9002302</v>
+        <v>1081.1113541</v>
       </c>
       <c r="O20">
-        <v>173.904036832</v>
+        <v>172.977816656</v>
       </c>
       <c r="P20">
-        <v>912.9961933679999</v>
+        <v>908.133537444</v>
       </c>
       <c r="Q20">
-        <v>1108.896193368</v>
+        <v>1104.033537444</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09553537216924217</v>
+        <v>0.09606644118685259</v>
       </c>
       <c r="T20">
-        <v>0.6846261185515247</v>
+        <v>0.6919364834759566</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.43092736467831</v>
+        <v>10.82929960864261</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08584169736135061</v>
+        <v>0.08573902954392264</v>
       </c>
       <c r="C21">
-        <v>9562.868684412628</v>
+        <v>9460.289247648601</v>
       </c>
       <c r="D21">
-        <v>11629.82168441263</v>
+        <v>11642.3292476486</v>
       </c>
       <c r="E21">
-        <v>2099.753</v>
+        <v>2214.84</v>
       </c>
       <c r="F21">
-        <v>2186.653</v>
+        <v>2301.74</v>
       </c>
       <c r="G21">
         <v>119.7</v>
@@ -2997,28 +2997,28 @@
         <v>1191.1</v>
       </c>
       <c r="M21">
-        <v>109.9886459</v>
+        <v>115.777522</v>
       </c>
       <c r="N21">
-        <v>1081.1113541</v>
+        <v>1075.322478</v>
       </c>
       <c r="O21">
-        <v>172.977816656</v>
+        <v>172.05159648</v>
       </c>
       <c r="P21">
-        <v>908.133537444</v>
+        <v>903.2708815200001</v>
       </c>
       <c r="Q21">
-        <v>1104.033537444</v>
+        <v>1099.17088152</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09606644118685259</v>
+        <v>0.0966107869299033</v>
       </c>
       <c r="T21">
-        <v>0.6919364834759566</v>
+        <v>0.6994296075234996</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.82929960864261</v>
+        <v>10.28783462821048</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08573902954392264</v>
+        <v>0.08563636172649468</v>
       </c>
       <c r="C22">
-        <v>9460.289247648601</v>
+        <v>9357.736742951052</v>
       </c>
       <c r="D22">
-        <v>11642.3292476486</v>
+        <v>11654.86374295105</v>
       </c>
       <c r="E22">
-        <v>2214.84</v>
+        <v>2329.927</v>
       </c>
       <c r="F22">
-        <v>2301.74</v>
+        <v>2416.827</v>
       </c>
       <c r="G22">
         <v>119.7</v>
@@ -3079,28 +3079,28 @@
         <v>1191.1</v>
       </c>
       <c r="M22">
-        <v>115.777522</v>
+        <v>121.5663981</v>
       </c>
       <c r="N22">
-        <v>1075.322478</v>
+        <v>1069.5336019</v>
       </c>
       <c r="O22">
-        <v>172.05159648</v>
+        <v>171.125376304</v>
       </c>
       <c r="P22">
-        <v>903.2708815200001</v>
+        <v>898.408225596</v>
       </c>
       <c r="Q22">
-        <v>1099.17088152</v>
+        <v>1094.308225596</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0966107869299033</v>
+        <v>0.09716891357784135</v>
       </c>
       <c r="T22">
-        <v>0.6994296075234996</v>
+        <v>0.7071124309140182</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.28783462821048</v>
+        <v>9.797937741152833</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08563636172649466</v>
+        <v>0.08553369390906669</v>
       </c>
       <c r="C23">
-        <v>9357.736742951056</v>
+        <v>9255.21125740145</v>
       </c>
       <c r="D23">
-        <v>11654.86374295105</v>
+        <v>11667.42525740145</v>
       </c>
       <c r="E23">
-        <v>2329.927</v>
+        <v>2445.014</v>
       </c>
       <c r="F23">
-        <v>2416.827</v>
+        <v>2531.914</v>
       </c>
       <c r="G23">
         <v>119.7</v>
@@ -3161,28 +3161,28 @@
         <v>1191.1</v>
       </c>
       <c r="M23">
-        <v>121.5663981</v>
+        <v>127.3552742</v>
       </c>
       <c r="N23">
-        <v>1069.5336019</v>
+        <v>1063.7447258</v>
       </c>
       <c r="O23">
-        <v>171.125376304</v>
+        <v>170.199156128</v>
       </c>
       <c r="P23">
-        <v>898.408225596</v>
+        <v>893.5455696719999</v>
       </c>
       <c r="Q23">
-        <v>1094.308225596</v>
+        <v>1089.445569672</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09716891357784135</v>
+        <v>0.09774135116547011</v>
       </c>
       <c r="T23">
-        <v>0.7071124309140182</v>
+        <v>0.7149922497760884</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.797937741152833</v>
+        <v>9.352576934736796</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08553369390906669</v>
+        <v>0.08543102609163872</v>
       </c>
       <c r="C24">
-        <v>9255.21125740145</v>
+        <v>9152.712878457087</v>
       </c>
       <c r="D24">
-        <v>11667.42525740145</v>
+        <v>11680.01387845709</v>
       </c>
       <c r="E24">
-        <v>2445.014</v>
+        <v>2560.101</v>
       </c>
       <c r="F24">
-        <v>2531.914</v>
+        <v>2647.001</v>
       </c>
       <c r="G24">
         <v>119.7</v>
@@ -3243,28 +3243,28 @@
         <v>1191.1</v>
       </c>
       <c r="M24">
-        <v>127.3552742</v>
+        <v>133.1441503</v>
       </c>
       <c r="N24">
-        <v>1063.7447258</v>
+        <v>1057.9558497</v>
       </c>
       <c r="O24">
-        <v>170.199156128</v>
+        <v>169.272935952</v>
       </c>
       <c r="P24">
-        <v>893.5455696719999</v>
+        <v>888.6829137479998</v>
       </c>
       <c r="Q24">
-        <v>1089.445569672</v>
+        <v>1084.582913748</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09774135116547011</v>
+        <v>0.09832865726186847</v>
       </c>
       <c r="T24">
-        <v>0.7149922497760884</v>
+        <v>0.723076739257953</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.352576934736796</v>
+        <v>8.945943154965629</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08543102609163872</v>
+        <v>0.08563075827421074</v>
       </c>
       <c r="C25">
-        <v>9152.712878457087</v>
+        <v>9013.160633296302</v>
       </c>
       <c r="D25">
-        <v>11680.01387845709</v>
+        <v>11655.5486332963</v>
       </c>
       <c r="E25">
-        <v>2560.101</v>
+        <v>2675.188</v>
       </c>
       <c r="F25">
-        <v>2647.001</v>
+        <v>2762.088</v>
       </c>
       <c r="G25">
         <v>119.7</v>
@@ -3325,45 +3325,45 @@
         <v>1191.1</v>
       </c>
       <c r="M25">
-        <v>133.1441503</v>
+        <v>143.0761584</v>
       </c>
       <c r="N25">
-        <v>1057.9558497</v>
+        <v>1048.0238416</v>
       </c>
       <c r="O25">
-        <v>169.272935952</v>
+        <v>167.683814656</v>
       </c>
       <c r="P25">
-        <v>888.6829137479998</v>
+        <v>880.340026944</v>
       </c>
       <c r="Q25">
-        <v>1084.582913748</v>
+        <v>1076.240026944</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09832865726186847</v>
+        <v>0.09893141878185624</v>
       </c>
       <c r="T25">
-        <v>0.723076739257953</v>
+        <v>0.7313739784630243</v>
       </c>
       <c r="U25">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V25">
         <v>0.16</v>
       </c>
       <c r="W25">
-        <v>0.042252</v>
+        <v>0.043512</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y25">
-        <v>8.945943154965629</v>
+        <v>8.324936965878166</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08563075827421074</v>
+        <v>0.08554069045678278</v>
       </c>
       <c r="C26">
-        <v>9013.160633296302</v>
+        <v>8909.093362808</v>
       </c>
       <c r="D26">
-        <v>11655.5486332963</v>
+        <v>11666.568362808</v>
       </c>
       <c r="E26">
-        <v>2675.188</v>
+        <v>2790.275</v>
       </c>
       <c r="F26">
-        <v>2762.088</v>
+        <v>2877.175</v>
       </c>
       <c r="G26">
         <v>119.7</v>
@@ -3407,28 +3407,28 @@
         <v>1191.1</v>
       </c>
       <c r="M26">
-        <v>143.0761584</v>
+        <v>149.037665</v>
       </c>
       <c r="N26">
-        <v>1048.0238416</v>
+        <v>1042.062335</v>
       </c>
       <c r="O26">
-        <v>167.683814656</v>
+        <v>166.7299736</v>
       </c>
       <c r="P26">
-        <v>880.340026944</v>
+        <v>875.3323613999999</v>
       </c>
       <c r="Q26">
-        <v>1076.240026944</v>
+        <v>1071.2323614</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09893141878185624</v>
+        <v>0.09955025394237704</v>
       </c>
       <c r="T26">
-        <v>0.7313739784630243</v>
+        <v>0.739892477380231</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.324936965878166</v>
+        <v>7.99193948724304</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08554069045678278</v>
+        <v>0.08545062263935481</v>
       </c>
       <c r="C27">
-        <v>8909.093362808</v>
+        <v>8805.046949228465</v>
       </c>
       <c r="D27">
-        <v>11666.568362808</v>
+        <v>11677.60894922846</v>
       </c>
       <c r="E27">
-        <v>2790.275</v>
+        <v>2905.362</v>
       </c>
       <c r="F27">
-        <v>2877.175</v>
+        <v>2992.262</v>
       </c>
       <c r="G27">
         <v>119.7</v>
@@ -3489,28 +3489,28 @@
         <v>1191.1</v>
       </c>
       <c r="M27">
-        <v>149.037665</v>
+        <v>154.9991716</v>
       </c>
       <c r="N27">
-        <v>1042.062335</v>
+        <v>1036.1008284</v>
       </c>
       <c r="O27">
-        <v>166.7299736</v>
+        <v>165.776132544</v>
       </c>
       <c r="P27">
-        <v>875.3323613999999</v>
+        <v>870.3246958559999</v>
       </c>
       <c r="Q27">
-        <v>1071.2323614</v>
+        <v>1066.224695856</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09955025394237704</v>
+        <v>0.1001858143775065</v>
       </c>
       <c r="T27">
-        <v>0.739892477380231</v>
+        <v>0.7486412059979026</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.99193948724304</v>
+        <v>7.684557199272154</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08545062263935481</v>
+        <v>0.08536055482192684</v>
       </c>
       <c r="C28">
-        <v>8805.046949228465</v>
+        <v>8701.021451827219</v>
       </c>
       <c r="D28">
-        <v>11677.60894922846</v>
+        <v>11688.67045182722</v>
       </c>
       <c r="E28">
-        <v>2905.362</v>
+        <v>3020.449</v>
       </c>
       <c r="F28">
-        <v>2992.262</v>
+        <v>3107.349</v>
       </c>
       <c r="G28">
         <v>119.7</v>
@@ -3571,28 +3571,28 @@
         <v>1191.1</v>
       </c>
       <c r="M28">
-        <v>154.9991716</v>
+        <v>160.9606782</v>
       </c>
       <c r="N28">
-        <v>1036.1008284</v>
+        <v>1030.1393218</v>
       </c>
       <c r="O28">
-        <v>165.776132544</v>
+        <v>164.822291488</v>
       </c>
       <c r="P28">
-        <v>870.3246958559999</v>
+        <v>865.3170303119998</v>
       </c>
       <c r="Q28">
-        <v>1066.224695856</v>
+        <v>1061.217030312</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1001858143775065</v>
+        <v>0.100838787427297</v>
       </c>
       <c r="T28">
-        <v>0.7486412059979026</v>
+        <v>0.757629625810579</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.684557199272154</v>
+        <v>7.399943969669481</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08536055482192684</v>
+        <v>0.08527048700449887</v>
       </c>
       <c r="C29">
-        <v>8701.021451827219</v>
+        <v>8597.016930098562</v>
       </c>
       <c r="D29">
-        <v>11688.67045182722</v>
+        <v>11699.75293009856</v>
       </c>
       <c r="E29">
-        <v>3020.449</v>
+        <v>3135.536</v>
       </c>
       <c r="F29">
-        <v>3107.349</v>
+        <v>3222.436</v>
       </c>
       <c r="G29">
         <v>119.7</v>
@@ -3653,28 +3653,28 @@
         <v>1191.1</v>
       </c>
       <c r="M29">
-        <v>160.9606782</v>
+        <v>166.9221848</v>
       </c>
       <c r="N29">
-        <v>1030.1393218</v>
+        <v>1024.1778152</v>
       </c>
       <c r="O29">
-        <v>164.822291488</v>
+        <v>163.868450432</v>
       </c>
       <c r="P29">
-        <v>865.3170303119998</v>
+        <v>860.3093647679999</v>
       </c>
       <c r="Q29">
-        <v>1061.217030312</v>
+        <v>1056.209364768</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.100838787427297</v>
+        <v>0.1015098986173595</v>
       </c>
       <c r="T29">
-        <v>0.757629625810579</v>
+        <v>0.7668677239513852</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.399943969669481</v>
+        <v>7.135660256467</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08527048700449887</v>
+        <v>0.08518041918707089</v>
       </c>
       <c r="C30">
-        <v>8597.016930098562</v>
+        <v>8493.033443762644</v>
       </c>
       <c r="D30">
-        <v>11699.75293009856</v>
+        <v>11710.85644376264</v>
       </c>
       <c r="E30">
-        <v>3135.536</v>
+        <v>3250.623</v>
       </c>
       <c r="F30">
-        <v>3222.436</v>
+        <v>3337.523</v>
       </c>
       <c r="G30">
         <v>119.7</v>
@@ -3735,28 +3735,28 @@
         <v>1191.1</v>
       </c>
       <c r="M30">
-        <v>166.9221848</v>
+        <v>172.8836914</v>
       </c>
       <c r="N30">
-        <v>1024.1778152</v>
+        <v>1018.2163086</v>
       </c>
       <c r="O30">
-        <v>163.868450432</v>
+        <v>162.914609376</v>
       </c>
       <c r="P30">
-        <v>860.3093647679999</v>
+        <v>855.301699224</v>
       </c>
       <c r="Q30">
-        <v>1056.209364768</v>
+        <v>1051.201699224</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1015098986173595</v>
+        <v>0.1021999143479872</v>
       </c>
       <c r="T30">
-        <v>0.7668677239513852</v>
+        <v>0.776366050208834</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.135660256467</v>
+        <v>6.889603006243999</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08518041918707089</v>
+        <v>0.0855187513696429</v>
       </c>
       <c r="C31">
-        <v>8493.033443762646</v>
+        <v>8336.34575026741</v>
       </c>
       <c r="D31">
-        <v>11710.85644376264</v>
+        <v>11669.25575026741</v>
       </c>
       <c r="E31">
-        <v>3250.622999999999</v>
+        <v>3365.71</v>
       </c>
       <c r="F31">
-        <v>3337.522999999999</v>
+        <v>3452.61</v>
       </c>
       <c r="G31">
         <v>119.7</v>
@@ -3817,45 +3817,45 @@
         <v>1191.1</v>
       </c>
       <c r="M31">
-        <v>172.8836913999999</v>
+        <v>184.714635</v>
       </c>
       <c r="N31">
-        <v>1018.2163086</v>
+        <v>1006.385365</v>
       </c>
       <c r="O31">
-        <v>162.914609376</v>
+        <v>161.0216584</v>
       </c>
       <c r="P31">
-        <v>855.301699224</v>
+        <v>845.3637065999999</v>
       </c>
       <c r="Q31">
-        <v>1051.201699224</v>
+        <v>1041.2637066</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1021999143479872</v>
+        <v>0.1029096448137756</v>
       </c>
       <c r="T31">
-        <v>0.7763660502088339</v>
+        <v>0.7861357572164953</v>
       </c>
       <c r="U31">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V31">
         <v>0.16</v>
       </c>
       <c r="W31">
-        <v>0.043512</v>
+        <v>0.04494</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>6.889603006244002</v>
+        <v>6.448325006840958</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0855187513696429</v>
+        <v>0.08544296355221494</v>
       </c>
       <c r="C32">
-        <v>8336.34575026741</v>
+        <v>8230.551770481479</v>
       </c>
       <c r="D32">
-        <v>11669.25575026741</v>
+        <v>11678.54877048148</v>
       </c>
       <c r="E32">
-        <v>3365.71</v>
+        <v>3480.797</v>
       </c>
       <c r="F32">
-        <v>3452.61</v>
+        <v>3567.697</v>
       </c>
       <c r="G32">
         <v>119.7</v>
@@ -3899,28 +3899,28 @@
         <v>1191.1</v>
       </c>
       <c r="M32">
-        <v>184.714635</v>
+        <v>190.8717895</v>
       </c>
       <c r="N32">
-        <v>1006.385365</v>
+        <v>1000.2282105</v>
       </c>
       <c r="O32">
-        <v>161.0216584</v>
+        <v>160.03651368</v>
       </c>
       <c r="P32">
-        <v>845.3637065999999</v>
+        <v>840.1916968199999</v>
       </c>
       <c r="Q32">
-        <v>1041.2637066</v>
+        <v>1036.09169682</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1029096448137756</v>
+        <v>0.1036399471771231</v>
       </c>
       <c r="T32">
-        <v>0.7861357572164953</v>
+        <v>0.7961886441374224</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.448325006840958</v>
+        <v>6.240314522749314</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08544296355221494</v>
+        <v>0.08536717573478697</v>
       </c>
       <c r="C33">
-        <v>8230.551770481479</v>
+        <v>8124.772603817459</v>
       </c>
       <c r="D33">
-        <v>11678.54877048148</v>
+        <v>11687.85660381746</v>
       </c>
       <c r="E33">
-        <v>3480.797</v>
+        <v>3595.884</v>
       </c>
       <c r="F33">
-        <v>3567.697</v>
+        <v>3682.784</v>
       </c>
       <c r="G33">
         <v>119.7</v>
@@ -3981,28 +3981,28 @@
         <v>1191.1</v>
       </c>
       <c r="M33">
-        <v>190.8717895</v>
+        <v>197.028944</v>
       </c>
       <c r="N33">
-        <v>1000.2282105</v>
+        <v>994.071056</v>
       </c>
       <c r="O33">
-        <v>160.03651368</v>
+        <v>159.05136896</v>
       </c>
       <c r="P33">
-        <v>840.1916968199999</v>
+        <v>835.01968704</v>
       </c>
       <c r="Q33">
-        <v>1036.09169682</v>
+        <v>1030.91968704</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1036399471771231</v>
+        <v>0.1043917290217456</v>
       </c>
       <c r="T33">
-        <v>0.7961886441374224</v>
+        <v>0.8065372042030826</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.240314522749314</v>
+        <v>6.045304693913399</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08536717573478697</v>
+        <v>0.085291387917359</v>
       </c>
       <c r="C34">
-        <v>8124.772603817459</v>
+        <v>8019.008285721886</v>
       </c>
       <c r="D34">
-        <v>11687.85660381746</v>
+        <v>11697.17928572188</v>
       </c>
       <c r="E34">
-        <v>3595.884</v>
+        <v>3710.971</v>
       </c>
       <c r="F34">
-        <v>3682.784</v>
+        <v>3797.871</v>
       </c>
       <c r="G34">
         <v>119.7</v>
@@ -4063,28 +4063,28 @@
         <v>1191.1</v>
       </c>
       <c r="M34">
-        <v>197.028944</v>
+        <v>203.1860985</v>
       </c>
       <c r="N34">
-        <v>994.071056</v>
+        <v>987.9139015</v>
       </c>
       <c r="O34">
-        <v>159.05136896</v>
+        <v>158.06622424</v>
       </c>
       <c r="P34">
-        <v>835.01968704</v>
+        <v>829.84767726</v>
       </c>
       <c r="Q34">
-        <v>1030.91968704</v>
+        <v>1025.74767726</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1043917290217456</v>
+        <v>0.1051659521154612</v>
       </c>
       <c r="T34">
-        <v>0.8065372042030826</v>
+        <v>0.8171946765095088</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.045304693913399</v>
+        <v>5.862113642582689</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.085291387917359</v>
+        <v>0.08521560009993104</v>
       </c>
       <c r="C35">
-        <v>8019.008285721886</v>
+        <v>7913.258851754488</v>
       </c>
       <c r="D35">
-        <v>11697.17928572188</v>
+        <v>11706.51685175449</v>
       </c>
       <c r="E35">
-        <v>3710.971</v>
+        <v>3826.058</v>
       </c>
       <c r="F35">
-        <v>3797.871</v>
+        <v>3912.958</v>
       </c>
       <c r="G35">
         <v>119.7</v>
@@ -4145,28 +4145,28 @@
         <v>1191.1</v>
       </c>
       <c r="M35">
-        <v>203.1860985</v>
+        <v>209.343253</v>
       </c>
       <c r="N35">
-        <v>987.9139015</v>
+        <v>981.7567469999999</v>
       </c>
       <c r="O35">
-        <v>158.06622424</v>
+        <v>157.08107952</v>
       </c>
       <c r="P35">
-        <v>829.84767726</v>
+        <v>824.6756674799999</v>
       </c>
       <c r="Q35">
-        <v>1025.74767726</v>
+        <v>1020.57566748</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1051659521154612</v>
+        <v>0.105963636515047</v>
       </c>
       <c r="T35">
-        <v>0.8171946765095088</v>
+        <v>0.8281751025221904</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.862113642582689</v>
+        <v>5.689698535447904</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08521560009993104</v>
+        <v>0.08537501228250305</v>
       </c>
       <c r="C36">
-        <v>7913.258851754488</v>
+        <v>7778.548475421925</v>
       </c>
       <c r="D36">
-        <v>11706.51685175449</v>
+        <v>11686.89347542192</v>
       </c>
       <c r="E36">
-        <v>3826.058</v>
+        <v>3941.145</v>
       </c>
       <c r="F36">
-        <v>3912.958</v>
+        <v>4028.045</v>
       </c>
       <c r="G36">
         <v>119.7</v>
@@ -4227,45 +4227,45 @@
         <v>1191.1</v>
       </c>
       <c r="M36">
-        <v>209.343253</v>
+        <v>218.7228435</v>
       </c>
       <c r="N36">
-        <v>981.7567469999999</v>
+        <v>972.3771565</v>
       </c>
       <c r="O36">
-        <v>157.08107952</v>
+        <v>155.58034504</v>
       </c>
       <c r="P36">
-        <v>824.6756674799999</v>
+        <v>816.79681146</v>
       </c>
       <c r="Q36">
-        <v>1020.57566748</v>
+        <v>1012.69681146</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.105963636515047</v>
+        <v>0.1067858650500047</v>
       </c>
       <c r="T36">
-        <v>0.8281751025221904</v>
+        <v>0.8394933877968005</v>
       </c>
       <c r="U36">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V36">
         <v>0.16</v>
       </c>
       <c r="W36">
-        <v>0.04494</v>
+        <v>0.045612</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y36">
-        <v>5.689698535447904</v>
+        <v>5.445704622983286</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08537501228250305</v>
+        <v>0.0853059444650751</v>
       </c>
       <c r="C37">
-        <v>7778.548475421925</v>
+        <v>7671.9555267152</v>
       </c>
       <c r="D37">
-        <v>11686.89347542192</v>
+        <v>11695.3875267152</v>
       </c>
       <c r="E37">
-        <v>3941.145</v>
+        <v>4056.232</v>
       </c>
       <c r="F37">
-        <v>4028.045</v>
+        <v>4143.132000000001</v>
       </c>
       <c r="G37">
         <v>119.7</v>
@@ -4309,28 +4309,28 @@
         <v>1191.1</v>
       </c>
       <c r="M37">
-        <v>218.7228435</v>
+        <v>224.9720676</v>
       </c>
       <c r="N37">
-        <v>972.3771565</v>
+        <v>966.1279323999998</v>
       </c>
       <c r="O37">
-        <v>155.58034504</v>
+        <v>154.580469184</v>
       </c>
       <c r="P37">
-        <v>816.79681146</v>
+        <v>811.5474632159999</v>
       </c>
       <c r="Q37">
-        <v>1012.69681146</v>
+        <v>1007.447463216</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1067858650500047</v>
+        <v>0.1076337882266798</v>
       </c>
       <c r="T37">
-        <v>0.8394933877968005</v>
+        <v>0.8511653694862423</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.445704622983286</v>
+        <v>5.294435050122639</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0853059444650751</v>
+        <v>0.08523687664764712</v>
       </c>
       <c r="C38">
-        <v>7671.955526715201</v>
+        <v>7565.37493396665</v>
       </c>
       <c r="D38">
-        <v>11695.3875267152</v>
+        <v>11703.89393396665</v>
       </c>
       <c r="E38">
-        <v>4056.232</v>
+        <v>4171.319</v>
       </c>
       <c r="F38">
-        <v>4143.132</v>
+        <v>4258.218999999999</v>
       </c>
       <c r="G38">
         <v>119.7</v>
@@ -4391,28 +4391,28 @@
         <v>1191.1</v>
       </c>
       <c r="M38">
-        <v>224.9720676</v>
+        <v>231.2212917</v>
       </c>
       <c r="N38">
-        <v>966.1279324</v>
+        <v>959.8787083</v>
       </c>
       <c r="O38">
-        <v>154.580469184</v>
+        <v>153.580593328</v>
       </c>
       <c r="P38">
-        <v>811.547463216</v>
+        <v>806.298114972</v>
       </c>
       <c r="Q38">
-        <v>1007.447463216</v>
+        <v>1002.198114972</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1076337882266798</v>
+        <v>0.1085086295994399</v>
       </c>
       <c r="T38">
-        <v>0.8511653694862422</v>
+        <v>0.8632078902769361</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.29443505012264</v>
+        <v>5.151342210930137</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08523687664764712</v>
+        <v>0.08516780883021914</v>
       </c>
       <c r="C39">
-        <v>7565.37493396665</v>
+        <v>7458.806724156469</v>
       </c>
       <c r="D39">
-        <v>11703.89393396665</v>
+        <v>11712.41272415647</v>
       </c>
       <c r="E39">
-        <v>4171.319</v>
+        <v>4286.406</v>
       </c>
       <c r="F39">
-        <v>4258.218999999999</v>
+        <v>4373.306</v>
       </c>
       <c r="G39">
         <v>119.7</v>
@@ -4473,28 +4473,28 @@
         <v>1191.1</v>
       </c>
       <c r="M39">
-        <v>231.2212917</v>
+        <v>237.4705158</v>
       </c>
       <c r="N39">
-        <v>959.8787083</v>
+        <v>953.6294842</v>
       </c>
       <c r="O39">
-        <v>153.580593328</v>
+        <v>152.580717472</v>
       </c>
       <c r="P39">
-        <v>806.298114972</v>
+        <v>801.0487667279999</v>
       </c>
       <c r="Q39">
-        <v>1002.198114972</v>
+        <v>996.9487667279999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1085086295994399</v>
+        <v>0.1094116916616438</v>
       </c>
       <c r="T39">
-        <v>0.8632078902769361</v>
+        <v>0.8756388794802329</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.151342210930137</v>
+        <v>5.015780573800396</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08516780883021914</v>
+        <v>0.08509874101279118</v>
       </c>
       <c r="C40">
-        <v>7458.806724156469</v>
+        <v>7352.250924343467</v>
       </c>
       <c r="D40">
-        <v>11712.41272415647</v>
+        <v>11720.94392434347</v>
       </c>
       <c r="E40">
-        <v>4286.406</v>
+        <v>4401.493</v>
       </c>
       <c r="F40">
-        <v>4373.306</v>
+        <v>4488.393</v>
       </c>
       <c r="G40">
         <v>119.7</v>
@@ -4555,28 +4555,28 @@
         <v>1191.1</v>
       </c>
       <c r="M40">
-        <v>237.4705158</v>
+        <v>243.7197399</v>
       </c>
       <c r="N40">
-        <v>953.6294842</v>
+        <v>947.3802600999999</v>
       </c>
       <c r="O40">
-        <v>152.580717472</v>
+        <v>151.580841616</v>
       </c>
       <c r="P40">
-        <v>801.0487667279999</v>
+        <v>795.7994184839999</v>
       </c>
       <c r="Q40">
-        <v>996.9487667279999</v>
+        <v>991.6994184839999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1094116916616438</v>
+        <v>0.1103443623160511</v>
       </c>
       <c r="T40">
-        <v>0.8756388794802329</v>
+        <v>0.8884774421000313</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.015780573800396</v>
+        <v>4.887170815497822</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08509874101279118</v>
+        <v>0.08502967319536321</v>
       </c>
       <c r="C41">
-        <v>7352.250924343467</v>
+        <v>7245.707561665358</v>
       </c>
       <c r="D41">
-        <v>11720.94392434347</v>
+        <v>11729.48756166536</v>
       </c>
       <c r="E41">
-        <v>4401.493</v>
+        <v>4516.58</v>
       </c>
       <c r="F41">
-        <v>4488.393</v>
+        <v>4603.48</v>
       </c>
       <c r="G41">
         <v>119.7</v>
@@ -4637,28 +4637,28 @@
         <v>1191.1</v>
       </c>
       <c r="M41">
-        <v>243.7197399</v>
+        <v>249.968964</v>
       </c>
       <c r="N41">
-        <v>947.3802600999999</v>
+        <v>941.131036</v>
       </c>
       <c r="O41">
-        <v>151.580841616</v>
+        <v>150.58096576</v>
       </c>
       <c r="P41">
-        <v>795.7994184839999</v>
+        <v>790.55007024</v>
       </c>
       <c r="Q41">
-        <v>991.6994184839999</v>
+        <v>986.4500702399999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1103443623160511</v>
+        <v>0.111308121992272</v>
       </c>
       <c r="T41">
-        <v>0.8884774421000313</v>
+        <v>0.9017439568071565</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.887170815497822</v>
+        <v>4.764991545110377</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08502967319536321</v>
+        <v>0.08496060537793523</v>
       </c>
       <c r="C42">
-        <v>7245.707561665358</v>
+        <v>7139.176663339033</v>
       </c>
       <c r="D42">
-        <v>11729.48756166536</v>
+        <v>11738.04366333903</v>
       </c>
       <c r="E42">
-        <v>4516.58</v>
+        <v>4631.667</v>
       </c>
       <c r="F42">
-        <v>4603.48</v>
+        <v>4718.567</v>
       </c>
       <c r="G42">
         <v>119.7</v>
@@ -4719,28 +4719,28 @@
         <v>1191.1</v>
       </c>
       <c r="M42">
-        <v>249.968964</v>
+        <v>256.2181881</v>
       </c>
       <c r="N42">
-        <v>941.131036</v>
+        <v>934.8818118999999</v>
       </c>
       <c r="O42">
-        <v>150.58096576</v>
+        <v>149.581089904</v>
       </c>
       <c r="P42">
-        <v>790.55007024</v>
+        <v>785.3007219959999</v>
       </c>
       <c r="Q42">
-        <v>986.4500702399999</v>
+        <v>981.2007219959999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.111308121992272</v>
+        <v>0.1123045514880258</v>
       </c>
       <c r="T42">
-        <v>0.9017439568071565</v>
+        <v>0.9154601838772348</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.764991545110377</v>
+        <v>4.648772239132073</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08496060537793523</v>
+        <v>0.08489153756050725</v>
       </c>
       <c r="C43">
-        <v>7139.176663339033</v>
+        <v>7032.658256660847</v>
       </c>
       <c r="D43">
-        <v>11738.04366333903</v>
+        <v>11746.61225666085</v>
       </c>
       <c r="E43">
-        <v>4631.667</v>
+        <v>4746.754000000001</v>
       </c>
       <c r="F43">
-        <v>4718.567</v>
+        <v>4833.654</v>
       </c>
       <c r="G43">
         <v>119.7</v>
@@ -4801,28 +4801,28 @@
         <v>1191.1</v>
       </c>
       <c r="M43">
-        <v>256.2181881</v>
+        <v>262.4674122</v>
       </c>
       <c r="N43">
-        <v>934.8818118999999</v>
+        <v>928.6325877999999</v>
       </c>
       <c r="O43">
-        <v>149.581089904</v>
+        <v>148.581214048</v>
       </c>
       <c r="P43">
-        <v>785.3007219959999</v>
+        <v>780.0513737519999</v>
       </c>
       <c r="Q43">
-        <v>981.2007219959999</v>
+        <v>975.9513737519999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1123045514880258</v>
+        <v>0.1133353406215643</v>
       </c>
       <c r="T43">
-        <v>0.9154601838772348</v>
+        <v>0.9296493842945573</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.648772239132073</v>
+        <v>4.538087185819405</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08489153756050727</v>
+        <v>0.0848224697430793</v>
       </c>
       <c r="C44">
-        <v>7032.658256660846</v>
+        <v>6926.152369006927</v>
       </c>
       <c r="D44">
-        <v>11746.61225666084</v>
+        <v>11755.19336900693</v>
       </c>
       <c r="E44">
-        <v>4746.754</v>
+        <v>4861.840999999999</v>
       </c>
       <c r="F44">
-        <v>4833.654</v>
+        <v>4948.740999999999</v>
       </c>
       <c r="G44">
         <v>119.7</v>
@@ -4883,28 +4883,28 @@
         <v>1191.1</v>
       </c>
       <c r="M44">
-        <v>262.4674122</v>
+        <v>268.7166362999999</v>
       </c>
       <c r="N44">
-        <v>928.6325878</v>
+        <v>922.3833637</v>
       </c>
       <c r="O44">
-        <v>148.581214048</v>
+        <v>147.581338192</v>
       </c>
       <c r="P44">
-        <v>780.051373752</v>
+        <v>774.802025508</v>
       </c>
       <c r="Q44">
-        <v>975.951373752</v>
+        <v>970.702025508</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1133353406215643</v>
+        <v>0.114402297794876</v>
       </c>
       <c r="T44">
-        <v>0.9296493842945573</v>
+        <v>0.9443364513931894</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.538087185819407</v>
+        <v>4.432550274521281</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0848224697430793</v>
+        <v>0.08475340192565133</v>
       </c>
       <c r="C45">
-        <v>6926.152369006927</v>
+        <v>6819.659027833453</v>
       </c>
       <c r="D45">
-        <v>11755.19336900693</v>
+        <v>11763.78702783345</v>
       </c>
       <c r="E45">
-        <v>4861.840999999999</v>
+        <v>4976.928</v>
       </c>
       <c r="F45">
-        <v>4948.740999999999</v>
+        <v>5063.828</v>
       </c>
       <c r="G45">
         <v>119.7</v>
@@ -4965,28 +4965,28 @@
         <v>1191.1</v>
       </c>
       <c r="M45">
-        <v>268.7166362999999</v>
+        <v>274.9658604</v>
       </c>
       <c r="N45">
-        <v>922.3833637</v>
+        <v>916.1341395999999</v>
       </c>
       <c r="O45">
-        <v>147.581338192</v>
+        <v>146.581462336</v>
       </c>
       <c r="P45">
-        <v>774.802025508</v>
+        <v>769.552677264</v>
       </c>
       <c r="Q45">
-        <v>970.702025508</v>
+        <v>965.4526772639999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.114402297794876</v>
+        <v>0.1155073605815202</v>
       </c>
       <c r="T45">
-        <v>0.9443364513931894</v>
+        <v>0.959548056602487</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.432550274521281</v>
+        <v>4.331810495554887</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08475340192565133</v>
+        <v>0.08506233410822335</v>
       </c>
       <c r="C46">
-        <v>6819.659027833453</v>
+        <v>6666.230879396081</v>
       </c>
       <c r="D46">
-        <v>11763.78702783345</v>
+        <v>11725.44587939608</v>
       </c>
       <c r="E46">
-        <v>4976.928</v>
+        <v>5092.015</v>
       </c>
       <c r="F46">
-        <v>5063.828</v>
+        <v>5178.915</v>
       </c>
       <c r="G46">
         <v>119.7</v>
@@ -5047,45 +5047,45 @@
         <v>1191.1</v>
       </c>
       <c r="M46">
-        <v>274.9658604</v>
+        <v>286.3939995</v>
       </c>
       <c r="N46">
-        <v>916.1341395999999</v>
+        <v>904.7060004999998</v>
       </c>
       <c r="O46">
-        <v>146.581462336</v>
+        <v>144.75296008</v>
       </c>
       <c r="P46">
-        <v>769.552677264</v>
+        <v>759.9530404199999</v>
       </c>
       <c r="Q46">
-        <v>965.4526772639999</v>
+        <v>955.8530404199998</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1155073605815202</v>
+        <v>0.116652607469497</v>
       </c>
       <c r="T46">
-        <v>0.959548056602487</v>
+        <v>0.9753128110921225</v>
       </c>
       <c r="U46">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V46">
         <v>0.16</v>
       </c>
       <c r="W46">
-        <v>0.045612</v>
+        <v>0.046452</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.331810495554887</v>
+        <v>4.15895585130791</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08506233410822335</v>
+        <v>0.08500166629079538</v>
       </c>
       <c r="C47">
-        <v>6666.230879396081</v>
+        <v>6558.653545148904</v>
       </c>
       <c r="D47">
-        <v>11725.44587939608</v>
+        <v>11732.9555451489</v>
       </c>
       <c r="E47">
-        <v>5092.015</v>
+        <v>5207.102</v>
       </c>
       <c r="F47">
-        <v>5178.915</v>
+        <v>5294.001999999999</v>
       </c>
       <c r="G47">
         <v>119.7</v>
@@ -5129,28 +5129,28 @@
         <v>1191.1</v>
       </c>
       <c r="M47">
-        <v>286.3939995</v>
+        <v>292.7583106</v>
       </c>
       <c r="N47">
-        <v>904.7060004999998</v>
+        <v>898.3416894</v>
       </c>
       <c r="O47">
-        <v>144.75296008</v>
+        <v>143.734670304</v>
       </c>
       <c r="P47">
-        <v>759.9530404199999</v>
+        <v>754.6070190959999</v>
       </c>
       <c r="Q47">
-        <v>955.8530404199998</v>
+        <v>950.5070190959999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.116652607469497</v>
+        <v>0.1178402709088803</v>
       </c>
       <c r="T47">
-        <v>0.9753128110921225</v>
+        <v>0.9916614453776706</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.15895585130791</v>
+        <v>4.068543767583826</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08500166629079538</v>
+        <v>0.08494099847336742</v>
       </c>
       <c r="C48">
-        <v>6558.653545148904</v>
+        <v>6451.085836330412</v>
       </c>
       <c r="D48">
-        <v>11732.9555451489</v>
+        <v>11740.47483633041</v>
       </c>
       <c r="E48">
-        <v>5207.102</v>
+        <v>5322.189</v>
       </c>
       <c r="F48">
-        <v>5294.001999999999</v>
+        <v>5409.089</v>
       </c>
       <c r="G48">
         <v>119.7</v>
@@ -5211,28 +5211,28 @@
         <v>1191.1</v>
       </c>
       <c r="M48">
-        <v>292.7583106</v>
+        <v>299.1226217</v>
       </c>
       <c r="N48">
-        <v>898.3416894</v>
+        <v>891.9773782999998</v>
       </c>
       <c r="O48">
-        <v>143.734670304</v>
+        <v>142.716380528</v>
       </c>
       <c r="P48">
-        <v>754.6070190959999</v>
+        <v>749.2609977719999</v>
       </c>
       <c r="Q48">
-        <v>950.5070190959999</v>
+        <v>945.1609977719999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1178402709088803</v>
+        <v>0.1190727518365423</v>
       </c>
       <c r="T48">
-        <v>0.9916614453776706</v>
+        <v>1.0086270092589</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.068543767583826</v>
+        <v>3.981979006571403</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08494099847336742</v>
+        <v>0.08488033065593945</v>
       </c>
       <c r="C49">
-        <v>6451.085836330412</v>
+        <v>6343.527771458412</v>
       </c>
       <c r="D49">
-        <v>11740.47483633041</v>
+        <v>11748.00377145841</v>
       </c>
       <c r="E49">
-        <v>5322.189</v>
+        <v>5437.276</v>
       </c>
       <c r="F49">
-        <v>5409.089</v>
+        <v>5524.175999999999</v>
       </c>
       <c r="G49">
         <v>119.7</v>
@@ -5293,28 +5293,28 @@
         <v>1191.1</v>
       </c>
       <c r="M49">
-        <v>299.1226217</v>
+        <v>305.4869328</v>
       </c>
       <c r="N49">
-        <v>891.9773782999998</v>
+        <v>885.6130671999999</v>
       </c>
       <c r="O49">
-        <v>142.716380528</v>
+        <v>141.698090752</v>
       </c>
       <c r="P49">
-        <v>749.2609977719999</v>
+        <v>743.9149764479999</v>
       </c>
       <c r="Q49">
-        <v>945.1609977719999</v>
+        <v>939.8149764479999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1190727518365423</v>
+        <v>0.1203526358768066</v>
       </c>
       <c r="T49">
-        <v>1.0086270092589</v>
+        <v>1.026245094827869</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.981979006571403</v>
+        <v>3.899021110601167</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08488033065593945</v>
+        <v>0.08481966283851147</v>
       </c>
       <c r="C50">
-        <v>6343.527771458412</v>
+        <v>6235.979369098215</v>
       </c>
       <c r="D50">
-        <v>11748.00377145841</v>
+        <v>11755.54236909821</v>
       </c>
       <c r="E50">
-        <v>5437.276</v>
+        <v>5552.362999999999</v>
       </c>
       <c r="F50">
-        <v>5524.175999999999</v>
+        <v>5639.262999999999</v>
       </c>
       <c r="G50">
         <v>119.7</v>
@@ -5375,28 +5375,28 @@
         <v>1191.1</v>
       </c>
       <c r="M50">
-        <v>305.4869328</v>
+        <v>311.8512438999999</v>
       </c>
       <c r="N50">
-        <v>885.6130671999999</v>
+        <v>879.2487561</v>
       </c>
       <c r="O50">
-        <v>141.698090752</v>
+        <v>140.679800976</v>
       </c>
       <c r="P50">
-        <v>743.9149764479999</v>
+        <v>738.568955124</v>
       </c>
       <c r="Q50">
-        <v>939.8149764479999</v>
+        <v>934.468955124</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1203526358768066</v>
+        <v>0.1216827114480617</v>
       </c>
       <c r="T50">
-        <v>1.026245094827868</v>
+        <v>1.044554085713267</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.899021110601167</v>
+        <v>3.819449251201144</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08481966283851147</v>
+        <v>0.08475899502108349</v>
       </c>
       <c r="C51">
-        <v>6235.979369098215</v>
+        <v>6128.440647862838</v>
       </c>
       <c r="D51">
-        <v>11755.54236909821</v>
+        <v>11763.09064786284</v>
       </c>
       <c r="E51">
-        <v>5552.362999999999</v>
+        <v>5667.45</v>
       </c>
       <c r="F51">
-        <v>5639.262999999999</v>
+        <v>5754.349999999999</v>
       </c>
       <c r="G51">
         <v>119.7</v>
@@ -5457,28 +5457,28 @@
         <v>1191.1</v>
       </c>
       <c r="M51">
-        <v>311.8512438999999</v>
+        <v>318.215555</v>
       </c>
       <c r="N51">
-        <v>879.2487561</v>
+        <v>872.8844449999999</v>
       </c>
       <c r="O51">
-        <v>140.679800976</v>
+        <v>139.6615112</v>
       </c>
       <c r="P51">
-        <v>738.568955124</v>
+        <v>733.2229338</v>
       </c>
       <c r="Q51">
-        <v>934.468955124</v>
+        <v>929.1229337999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1216827114480617</v>
+        <v>0.123065990042167</v>
       </c>
       <c r="T51">
-        <v>1.044554085713267</v>
+        <v>1.063595436234082</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.819449251201144</v>
+        <v>3.74306026617712</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08475899502108349</v>
+        <v>0.08469832720365553</v>
       </c>
       <c r="C52">
-        <v>6128.440647862838</v>
+        <v>6020.911626413119</v>
       </c>
       <c r="D52">
-        <v>11763.09064786284</v>
+        <v>11770.64862641312</v>
       </c>
       <c r="E52">
-        <v>5667.45</v>
+        <v>5782.537</v>
       </c>
       <c r="F52">
-        <v>5754.349999999999</v>
+        <v>5869.437</v>
       </c>
       <c r="G52">
         <v>119.7</v>
@@ -5539,28 +5539,28 @@
         <v>1191.1</v>
       </c>
       <c r="M52">
-        <v>318.215555</v>
+        <v>324.5798661</v>
       </c>
       <c r="N52">
-        <v>872.8844449999999</v>
+        <v>866.5201338999999</v>
       </c>
       <c r="O52">
-        <v>139.6615112</v>
+        <v>138.643221424</v>
       </c>
       <c r="P52">
-        <v>733.2229338</v>
+        <v>727.8769124759999</v>
       </c>
       <c r="Q52">
-        <v>929.1229337999999</v>
+        <v>923.7769124759999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.123065990042167</v>
+        <v>0.1245057289870521</v>
       </c>
       <c r="T52">
-        <v>1.063595436234082</v>
+        <v>1.083413984735338</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.74306026617712</v>
+        <v>3.669666927624627</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08469832720365553</v>
+        <v>0.08463765938622755</v>
       </c>
       <c r="C53">
-        <v>6020.911626413119</v>
+        <v>5913.392323457898</v>
       </c>
       <c r="D53">
-        <v>11770.64862641312</v>
+        <v>11778.2163234579</v>
       </c>
       <c r="E53">
-        <v>5782.537</v>
+        <v>5897.624</v>
       </c>
       <c r="F53">
-        <v>5869.437</v>
+        <v>5984.523999999999</v>
       </c>
       <c r="G53">
         <v>119.7</v>
@@ -5621,28 +5621,28 @@
         <v>1191.1</v>
       </c>
       <c r="M53">
-        <v>324.5798661</v>
+        <v>330.9441772</v>
       </c>
       <c r="N53">
-        <v>866.5201338999999</v>
+        <v>860.1558227999999</v>
       </c>
       <c r="O53">
-        <v>138.643221424</v>
+        <v>137.624931648</v>
       </c>
       <c r="P53">
-        <v>727.8769124759999</v>
+        <v>722.5308911519999</v>
       </c>
       <c r="Q53">
-        <v>923.7769124759999</v>
+        <v>918.4308911519998</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1245057289870521</v>
+        <v>0.1260054570546408</v>
       </c>
       <c r="T53">
-        <v>1.083413984735338</v>
+        <v>1.104058306090814</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.669666927624627</v>
+        <v>3.599096409785692</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08463765938622755</v>
+        <v>0.08457699156879959</v>
       </c>
       <c r="C54">
-        <v>5913.392323457898</v>
+        <v>5805.882757754148</v>
       </c>
       <c r="D54">
-        <v>11778.2163234579</v>
+        <v>11785.79375775415</v>
       </c>
       <c r="E54">
-        <v>5897.624</v>
+        <v>6012.711</v>
       </c>
       <c r="F54">
-        <v>5984.523999999999</v>
+        <v>6099.611</v>
       </c>
       <c r="G54">
         <v>119.7</v>
@@ -5703,28 +5703,28 @@
         <v>1191.1</v>
       </c>
       <c r="M54">
-        <v>330.9441772</v>
+        <v>337.3084883</v>
       </c>
       <c r="N54">
-        <v>860.1558227999999</v>
+        <v>853.7915116999999</v>
       </c>
       <c r="O54">
-        <v>137.624931648</v>
+        <v>136.606641872</v>
       </c>
       <c r="P54">
-        <v>722.5308911519999</v>
+        <v>717.1848698279999</v>
       </c>
       <c r="Q54">
-        <v>918.4308911519998</v>
+        <v>913.0848698279999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1260054570546408</v>
+        <v>0.1275690033378715</v>
       </c>
       <c r="T54">
-        <v>1.104058306090814</v>
+        <v>1.125581109206096</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.599096409785692</v>
+        <v>3.531188930355773</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08457699156879959</v>
+        <v>0.08451632375137161</v>
       </c>
       <c r="C55">
-        <v>5805.882757754148</v>
+        <v>5698.382948107154</v>
       </c>
       <c r="D55">
-        <v>11785.79375775415</v>
+        <v>11793.38094810715</v>
       </c>
       <c r="E55">
-        <v>6012.711</v>
+        <v>6127.798</v>
       </c>
       <c r="F55">
-        <v>6099.611</v>
+        <v>6214.697999999999</v>
       </c>
       <c r="G55">
         <v>119.7</v>
@@ -5785,28 +5785,28 @@
         <v>1191.1</v>
       </c>
       <c r="M55">
-        <v>337.3084883</v>
+        <v>343.6727994</v>
       </c>
       <c r="N55">
-        <v>853.7915116999999</v>
+        <v>847.4272005999999</v>
       </c>
       <c r="O55">
-        <v>136.606641872</v>
+        <v>135.588352096</v>
       </c>
       <c r="P55">
-        <v>717.1848698279999</v>
+        <v>711.8388485039999</v>
       </c>
       <c r="Q55">
-        <v>913.0848698279999</v>
+        <v>907.7388485039999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1275690033378715</v>
+        <v>0.1292005298942861</v>
       </c>
       <c r="T55">
-        <v>1.125581109206096</v>
+        <v>1.148039686369869</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.531188930355773</v>
+        <v>3.465796542756593</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08451632375137161</v>
+        <v>0.08445565593394364</v>
       </c>
       <c r="C56">
-        <v>5698.382948107154</v>
+        <v>5590.892913370648</v>
       </c>
       <c r="D56">
-        <v>11793.38094810715</v>
+        <v>11800.97791337065</v>
       </c>
       <c r="E56">
-        <v>6127.798</v>
+        <v>6242.885</v>
       </c>
       <c r="F56">
-        <v>6214.697999999999</v>
+        <v>6329.785</v>
       </c>
       <c r="G56">
         <v>119.7</v>
@@ -5867,28 +5867,28 @@
         <v>1191.1</v>
       </c>
       <c r="M56">
-        <v>343.6727994</v>
+        <v>350.0371105</v>
       </c>
       <c r="N56">
-        <v>847.4272005999999</v>
+        <v>841.0628895</v>
       </c>
       <c r="O56">
-        <v>135.588352096</v>
+        <v>134.57006232</v>
       </c>
       <c r="P56">
-        <v>711.8388485039999</v>
+        <v>706.4928271799999</v>
       </c>
       <c r="Q56">
-        <v>907.7388485039999</v>
+        <v>902.3928271799999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1292005298942861</v>
+        <v>0.130904568742097</v>
       </c>
       <c r="T56">
-        <v>1.148039686369869</v>
+        <v>1.171496422518699</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.465796542756593</v>
+        <v>3.402782060161018</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08445565593394364</v>
+        <v>0.08439498811651568</v>
       </c>
       <c r="C57">
-        <v>5590.892913370648</v>
+        <v>5483.412672446972</v>
       </c>
       <c r="D57">
-        <v>11800.97791337065</v>
+        <v>11808.58467244697</v>
       </c>
       <c r="E57">
-        <v>6242.885</v>
+        <v>6357.972000000001</v>
       </c>
       <c r="F57">
-        <v>6329.785</v>
+        <v>6444.872</v>
       </c>
       <c r="G57">
         <v>119.7</v>
@@ -5949,28 +5949,28 @@
         <v>1191.1</v>
       </c>
       <c r="M57">
-        <v>350.0371105</v>
+        <v>356.4014216</v>
       </c>
       <c r="N57">
-        <v>841.0628895</v>
+        <v>834.6985783999999</v>
       </c>
       <c r="O57">
-        <v>134.57006232</v>
+        <v>133.551772544</v>
       </c>
       <c r="P57">
-        <v>706.4928271799999</v>
+        <v>701.1468058559999</v>
       </c>
       <c r="Q57">
-        <v>902.3928271799999</v>
+        <v>897.0468058559999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.130904568742097</v>
+        <v>0.132686063901172</v>
       </c>
       <c r="T57">
-        <v>1.171496422518699</v>
+        <v>1.196019373947021</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.402782060161018</v>
+        <v>3.342018094800999</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08439498811651568</v>
+        <v>0.08433432029908769</v>
       </c>
       <c r="C58">
-        <v>5483.412672446972</v>
+        <v>5375.94224428725</v>
       </c>
       <c r="D58">
-        <v>11808.58467244697</v>
+        <v>11816.20124428725</v>
       </c>
       <c r="E58">
-        <v>6357.972000000001</v>
+        <v>6473.059</v>
       </c>
       <c r="F58">
-        <v>6444.872</v>
+        <v>6559.959</v>
       </c>
       <c r="G58">
         <v>119.7</v>
@@ -6031,28 +6031,28 @@
         <v>1191.1</v>
       </c>
       <c r="M58">
-        <v>356.4014216</v>
+        <v>362.7657327</v>
       </c>
       <c r="N58">
-        <v>834.6985783999999</v>
+        <v>828.3342673</v>
       </c>
       <c r="O58">
-        <v>133.551772544</v>
+        <v>132.533482768</v>
       </c>
       <c r="P58">
-        <v>701.1468058559999</v>
+        <v>695.800784532</v>
       </c>
       <c r="Q58">
-        <v>897.0468058559999</v>
+        <v>891.7007845319999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.132686063901172</v>
+        <v>0.1345504193002039</v>
       </c>
       <c r="T58">
-        <v>1.196019373947021</v>
+        <v>1.221682927767358</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.342018094800999</v>
+        <v>3.283386198400982</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08433432029908769</v>
+        <v>0.08427365248165973</v>
       </c>
       <c r="C59">
-        <v>5375.94224428725</v>
+        <v>5268.481647891513</v>
       </c>
       <c r="D59">
-        <v>11816.20124428725</v>
+        <v>11823.82764789151</v>
       </c>
       <c r="E59">
-        <v>6473.059</v>
+        <v>6588.146000000001</v>
       </c>
       <c r="F59">
-        <v>6559.959</v>
+        <v>6675.046</v>
       </c>
       <c r="G59">
         <v>119.7</v>
@@ -6113,28 +6113,28 @@
         <v>1191.1</v>
       </c>
       <c r="M59">
-        <v>362.7657327</v>
+        <v>369.1300438</v>
       </c>
       <c r="N59">
-        <v>828.3342673</v>
+        <v>821.9699561999998</v>
       </c>
       <c r="O59">
-        <v>132.533482768</v>
+        <v>131.515192992</v>
       </c>
       <c r="P59">
-        <v>695.800784532</v>
+        <v>690.4547632079998</v>
       </c>
       <c r="Q59">
-        <v>891.7007845319999</v>
+        <v>886.3547632079998</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1345504193002039</v>
+        <v>0.1365035535277613</v>
       </c>
       <c r="T59">
-        <v>1.221682927767358</v>
+        <v>1.24856855557914</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.283386198400982</v>
+        <v>3.226776091531999</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08427365248165972</v>
+        <v>0.08421298466423176</v>
       </c>
       <c r="C60">
-        <v>5268.481647891516</v>
+        <v>5161.030902308889</v>
       </c>
       <c r="D60">
-        <v>11823.82764789151</v>
+        <v>11831.46390230889</v>
       </c>
       <c r="E60">
-        <v>6588.145999999999</v>
+        <v>6703.232999999999</v>
       </c>
       <c r="F60">
-        <v>6675.045999999998</v>
+        <v>6790.132999999999</v>
       </c>
       <c r="G60">
         <v>119.7</v>
@@ -6195,28 +6195,28 @@
         <v>1191.1</v>
       </c>
       <c r="M60">
-        <v>369.1300438</v>
+        <v>375.4943549</v>
       </c>
       <c r="N60">
-        <v>821.9699562</v>
+        <v>815.6056450999999</v>
       </c>
       <c r="O60">
-        <v>131.515192992</v>
+        <v>130.496903216</v>
       </c>
       <c r="P60">
-        <v>690.454763208</v>
+        <v>685.108741884</v>
       </c>
       <c r="Q60">
-        <v>886.354763208</v>
+        <v>881.008741884</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1365035535277612</v>
+        <v>0.1385519625956872</v>
       </c>
       <c r="T60">
-        <v>1.248568555579139</v>
+        <v>1.27676567743052</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.226776091532</v>
+        <v>3.172084971336543</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08421298466423176</v>
+        <v>0.08415231684680378</v>
       </c>
       <c r="C61">
-        <v>5161.030902308889</v>
+        <v>5053.590026637743</v>
       </c>
       <c r="D61">
-        <v>11831.46390230889</v>
+        <v>11839.11002663774</v>
       </c>
       <c r="E61">
-        <v>6703.232999999999</v>
+        <v>6818.32</v>
       </c>
       <c r="F61">
-        <v>6790.132999999999</v>
+        <v>6905.219999999999</v>
       </c>
       <c r="G61">
         <v>119.7</v>
@@ -6277,28 +6277,28 @@
         <v>1191.1</v>
       </c>
       <c r="M61">
-        <v>375.4943549</v>
+        <v>381.858666</v>
       </c>
       <c r="N61">
-        <v>815.6056450999999</v>
+        <v>809.2413339999999</v>
       </c>
       <c r="O61">
-        <v>130.496903216</v>
+        <v>129.47861344</v>
       </c>
       <c r="P61">
-        <v>685.108741884</v>
+        <v>679.7627205599999</v>
       </c>
       <c r="Q61">
-        <v>881.008741884</v>
+        <v>875.6627205599999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1385519625956872</v>
+        <v>0.1407027921170095</v>
       </c>
       <c r="T61">
-        <v>1.27676567743052</v>
+        <v>1.30637265537447</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.172084971336543</v>
+        <v>3.119216888480933</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08415231684680378</v>
+        <v>0.08409164902937581</v>
       </c>
       <c r="C62">
-        <v>5053.590026637743</v>
+        <v>4946.159040025841</v>
       </c>
       <c r="D62">
-        <v>11839.11002663774</v>
+        <v>11846.76604002584</v>
       </c>
       <c r="E62">
-        <v>6818.32</v>
+        <v>6933.406999999999</v>
       </c>
       <c r="F62">
-        <v>6905.219999999999</v>
+        <v>7020.306999999999</v>
       </c>
       <c r="G62">
         <v>119.7</v>
@@ -6359,28 +6359,28 @@
         <v>1191.1</v>
       </c>
       <c r="M62">
-        <v>381.858666</v>
+        <v>388.2229770999999</v>
       </c>
       <c r="N62">
-        <v>809.2413339999999</v>
+        <v>802.8770228999999</v>
       </c>
       <c r="O62">
-        <v>129.47861344</v>
+        <v>128.460323664</v>
       </c>
       <c r="P62">
-        <v>679.7627205599999</v>
+        <v>674.4166992359999</v>
       </c>
       <c r="Q62">
-        <v>875.6627205599999</v>
+        <v>870.3166992359999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1407027921170095</v>
+        <v>0.1429639205881431</v>
       </c>
       <c r="T62">
-        <v>1.30637265537447</v>
+        <v>1.337497939879648</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.119216888480933</v>
+        <v>3.068082185391082</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08409164902937581</v>
+        <v>0.08403098121194784</v>
       </c>
       <c r="C63">
-        <v>4946.159040025841</v>
+        <v>4838.737961670508</v>
       </c>
       <c r="D63">
-        <v>11846.76604002584</v>
+        <v>11854.43196167051</v>
       </c>
       <c r="E63">
-        <v>6933.406999999999</v>
+        <v>7048.494</v>
       </c>
       <c r="F63">
-        <v>7020.306999999999</v>
+        <v>7135.393999999999</v>
       </c>
       <c r="G63">
         <v>119.7</v>
@@ -6441,28 +6441,28 @@
         <v>1191.1</v>
       </c>
       <c r="M63">
-        <v>388.2229770999999</v>
+        <v>394.5872882</v>
       </c>
       <c r="N63">
-        <v>802.8770228999999</v>
+        <v>796.5127117999999</v>
       </c>
       <c r="O63">
-        <v>128.460323664</v>
+        <v>127.442033888</v>
       </c>
       <c r="P63">
-        <v>674.4166992359999</v>
+        <v>669.070677912</v>
       </c>
       <c r="Q63">
-        <v>870.3166992359999</v>
+        <v>864.9706779119999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1429639205881431</v>
+        <v>0.1453440558209154</v>
       </c>
       <c r="T63">
-        <v>1.337497939879648</v>
+        <v>1.37026139725352</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.068082185391082</v>
+        <v>3.018596988852516</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08403098121194784</v>
+        <v>0.08529331339451987</v>
       </c>
       <c r="C64">
-        <v>4838.737961670508</v>
+        <v>4566.161248085247</v>
       </c>
       <c r="D64">
-        <v>11854.43196167051</v>
+        <v>11696.94224808525</v>
       </c>
       <c r="E64">
-        <v>7048.494</v>
+        <v>7163.581</v>
       </c>
       <c r="F64">
-        <v>7135.393999999999</v>
+        <v>7250.481</v>
       </c>
       <c r="G64">
         <v>119.7</v>
@@ -6523,45 +6523,45 @@
         <v>1191.1</v>
       </c>
       <c r="M64">
-        <v>394.5872882</v>
+        <v>419.0778018</v>
       </c>
       <c r="N64">
-        <v>796.5127117999999</v>
+        <v>772.0221981999998</v>
       </c>
       <c r="O64">
-        <v>127.442033888</v>
+        <v>123.523551712</v>
       </c>
       <c r="P64">
-        <v>669.070677912</v>
+        <v>648.4986464879998</v>
       </c>
       <c r="Q64">
-        <v>864.9706779119999</v>
+        <v>844.3986464879998</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1453440558209154</v>
+        <v>0.1478528470122159</v>
       </c>
       <c r="T64">
-        <v>1.37026139725352</v>
+        <v>1.404795852323276</v>
       </c>
       <c r="U64">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V64">
         <v>0.16</v>
       </c>
       <c r="W64">
-        <v>0.046452</v>
+        <v>0.048552</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y64">
-        <v>3.018596988852516</v>
+        <v>2.842193012572015</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08529331339451987</v>
+        <v>0.0852536455770919</v>
       </c>
       <c r="C65">
-        <v>4566.161248085247</v>
+        <v>4455.959531781564</v>
       </c>
       <c r="D65">
-        <v>11696.94224808525</v>
+        <v>11701.82753178156</v>
       </c>
       <c r="E65">
-        <v>7163.581</v>
+        <v>7278.668</v>
       </c>
       <c r="F65">
-        <v>7250.481</v>
+        <v>7365.567999999999</v>
       </c>
       <c r="G65">
         <v>119.7</v>
@@ -6605,28 +6605,28 @@
         <v>1191.1</v>
       </c>
       <c r="M65">
-        <v>419.0778018</v>
+        <v>425.7298304</v>
       </c>
       <c r="N65">
-        <v>772.0221981999998</v>
+        <v>765.3701695999999</v>
       </c>
       <c r="O65">
-        <v>123.523551712</v>
+        <v>122.459227136</v>
       </c>
       <c r="P65">
-        <v>648.4986464879998</v>
+        <v>642.910942464</v>
       </c>
       <c r="Q65">
-        <v>844.3986464879998</v>
+        <v>838.8109424639999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1478528470122159</v>
+        <v>0.1505010154919219</v>
       </c>
       <c r="T65">
-        <v>1.404795852323276</v>
+        <v>1.441248888230241</v>
       </c>
       <c r="U65">
         <v>0.0578</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.842193012572015</v>
+        <v>2.797783746750578</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.0852536455770919</v>
+        <v>0.08521397775966394</v>
       </c>
       <c r="C66">
-        <v>4455.959531781564</v>
+        <v>4345.76189790698</v>
       </c>
       <c r="D66">
-        <v>11701.82753178156</v>
+        <v>11706.71689790698</v>
       </c>
       <c r="E66">
-        <v>7278.668</v>
+        <v>7393.755</v>
       </c>
       <c r="F66">
-        <v>7365.567999999999</v>
+        <v>7480.655</v>
       </c>
       <c r="G66">
         <v>119.7</v>
@@ -6687,28 +6687,28 @@
         <v>1191.1</v>
       </c>
       <c r="M66">
-        <v>425.7298304</v>
+        <v>432.381859</v>
       </c>
       <c r="N66">
-        <v>765.3701695999999</v>
+        <v>758.7181409999998</v>
       </c>
       <c r="O66">
-        <v>122.459227136</v>
+        <v>121.39490256</v>
       </c>
       <c r="P66">
-        <v>642.910942464</v>
+        <v>637.3232384399998</v>
       </c>
       <c r="Q66">
-        <v>838.8109424639999</v>
+        <v>833.2232384399998</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1505010154919219</v>
+        <v>0.1533005078847541</v>
       </c>
       <c r="T66">
-        <v>1.441248888230241</v>
+        <v>1.479784954760462</v>
       </c>
       <c r="U66">
         <v>0.0578</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.797783746750578</v>
+        <v>2.754740919877491</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08521397775966394</v>
+        <v>0.08517430994223596</v>
       </c>
       <c r="C67">
-        <v>4345.76189790698</v>
+        <v>4235.568351580911</v>
       </c>
       <c r="D67">
-        <v>11706.71689790698</v>
+        <v>11711.61035158091</v>
       </c>
       <c r="E67">
-        <v>7393.755</v>
+        <v>7508.842</v>
       </c>
       <c r="F67">
-        <v>7480.655</v>
+        <v>7595.741999999999</v>
       </c>
       <c r="G67">
         <v>119.7</v>
@@ -6769,28 +6769,28 @@
         <v>1191.1</v>
       </c>
       <c r="M67">
-        <v>432.381859</v>
+        <v>439.0338876</v>
       </c>
       <c r="N67">
-        <v>758.7181409999998</v>
+        <v>752.0661123999998</v>
       </c>
       <c r="O67">
-        <v>121.39490256</v>
+        <v>120.330577984</v>
       </c>
       <c r="P67">
-        <v>637.3232384399998</v>
+        <v>631.7355344159998</v>
       </c>
       <c r="Q67">
-        <v>833.2232384399998</v>
+        <v>827.6355344159998</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1533005078847541</v>
+        <v>0.156264676300694</v>
       </c>
       <c r="T67">
-        <v>1.479784954760462</v>
+        <v>1.520587848733637</v>
       </c>
       <c r="U67">
         <v>0.0578</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.754740919877491</v>
+        <v>2.713002421091469</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08517430994223596</v>
+        <v>0.08513464212480799</v>
       </c>
       <c r="C68">
-        <v>4235.568351580911</v>
+        <v>4125.378897931334</v>
       </c>
       <c r="D68">
-        <v>11711.61035158091</v>
+        <v>11716.50789793133</v>
       </c>
       <c r="E68">
-        <v>7508.842</v>
+        <v>7623.929</v>
       </c>
       <c r="F68">
-        <v>7595.741999999999</v>
+        <v>7710.829</v>
       </c>
       <c r="G68">
         <v>119.7</v>
@@ -6851,28 +6851,28 @@
         <v>1191.1</v>
       </c>
       <c r="M68">
-        <v>439.0338876</v>
+        <v>445.6859162</v>
       </c>
       <c r="N68">
-        <v>752.0661123999998</v>
+        <v>745.4140837999998</v>
       </c>
       <c r="O68">
-        <v>120.330577984</v>
+        <v>119.266253408</v>
       </c>
       <c r="P68">
-        <v>631.7355344159998</v>
+        <v>626.1478303919998</v>
       </c>
       <c r="Q68">
-        <v>827.6355344159998</v>
+        <v>822.0478303919998</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.156264676300694</v>
+        <v>0.1594084912872969</v>
       </c>
       <c r="T68">
-        <v>1.520587848733637</v>
+        <v>1.563863645371852</v>
       </c>
       <c r="U68">
         <v>0.0578</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.713002421091469</v>
+        <v>2.672509847642343</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08513464212480799</v>
+        <v>0.08509497430738001</v>
       </c>
       <c r="C69">
-        <v>4125.378897931334</v>
+        <v>4015.193542094806</v>
       </c>
       <c r="D69">
-        <v>11716.50789793133</v>
+        <v>11721.40954209481</v>
       </c>
       <c r="E69">
-        <v>7623.929</v>
+        <v>7739.016000000001</v>
       </c>
       <c r="F69">
-        <v>7710.829</v>
+        <v>7825.916</v>
       </c>
       <c r="G69">
         <v>119.7</v>
@@ -6933,28 +6933,28 @@
         <v>1191.1</v>
       </c>
       <c r="M69">
-        <v>445.6859162</v>
+        <v>452.3379448000001</v>
       </c>
       <c r="N69">
-        <v>745.4140837999998</v>
+        <v>738.7620551999998</v>
       </c>
       <c r="O69">
-        <v>119.266253408</v>
+        <v>118.201928832</v>
       </c>
       <c r="P69">
-        <v>626.1478303919998</v>
+        <v>620.5601263679998</v>
       </c>
       <c r="Q69">
-        <v>822.0478303919998</v>
+        <v>816.4601263679998</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1594084912872969</v>
+        <v>0.1627487947105626</v>
       </c>
       <c r="T69">
-        <v>1.563863645371852</v>
+        <v>1.609844179299956</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.672509847642343</v>
+        <v>2.633208232235837</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08509497430738001</v>
+        <v>0.08505530648995205</v>
       </c>
       <c r="C70">
-        <v>4015.193542094806</v>
+        <v>3905.012289216488</v>
       </c>
       <c r="D70">
-        <v>11721.40954209481</v>
+        <v>11726.31528921649</v>
       </c>
       <c r="E70">
-        <v>7739.016000000001</v>
+        <v>7854.103</v>
       </c>
       <c r="F70">
-        <v>7825.916</v>
+        <v>7941.003</v>
       </c>
       <c r="G70">
         <v>119.7</v>
@@ -7015,28 +7015,28 @@
         <v>1191.1</v>
       </c>
       <c r="M70">
-        <v>452.3379448000001</v>
+        <v>458.9899734</v>
       </c>
       <c r="N70">
-        <v>738.7620551999998</v>
+        <v>732.1100265999999</v>
       </c>
       <c r="O70">
-        <v>118.201928832</v>
+        <v>117.137604256</v>
       </c>
       <c r="P70">
-        <v>620.5601263679998</v>
+        <v>614.9724223439998</v>
       </c>
       <c r="Q70">
-        <v>816.4601263679998</v>
+        <v>810.8724223439998</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1627487947105626</v>
+        <v>0.1663046015804905</v>
       </c>
       <c r="T70">
-        <v>1.609844179299956</v>
+        <v>1.658791199287937</v>
       </c>
       <c r="U70">
         <v>0.0578</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.633208232235837</v>
+        <v>2.595045794087492</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08505530648995205</v>
+        <v>0.08501563867252407</v>
       </c>
       <c r="C71">
-        <v>3905.012289216488</v>
+        <v>3794.835144450153</v>
       </c>
       <c r="D71">
-        <v>11726.31528921649</v>
+        <v>11731.22514445015</v>
       </c>
       <c r="E71">
-        <v>7854.103</v>
+        <v>7969.190000000001</v>
       </c>
       <c r="F71">
-        <v>7941.003</v>
+        <v>8056.09</v>
       </c>
       <c r="G71">
         <v>119.7</v>
@@ -7097,28 +7097,28 @@
         <v>1191.1</v>
       </c>
       <c r="M71">
-        <v>458.9899734</v>
+        <v>465.642002</v>
       </c>
       <c r="N71">
-        <v>732.1100265999999</v>
+        <v>725.4579979999999</v>
       </c>
       <c r="O71">
-        <v>117.137604256</v>
+        <v>116.07327968</v>
       </c>
       <c r="P71">
-        <v>614.9724223439998</v>
+        <v>609.3847183199998</v>
       </c>
       <c r="Q71">
-        <v>810.8724223439998</v>
+        <v>805.2847183199998</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1663046015804905</v>
+        <v>0.1700974622417469</v>
       </c>
       <c r="T71">
-        <v>1.658791199287937</v>
+        <v>1.711001353941784</v>
       </c>
       <c r="U71">
         <v>0.0578</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.595045794087492</v>
+        <v>2.557973711314814</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08501563867252407</v>
+        <v>0.08497597085509612</v>
       </c>
       <c r="C72">
-        <v>3794.835144450153</v>
+        <v>3684.662112958209</v>
       </c>
       <c r="D72">
-        <v>11731.22514445015</v>
+        <v>11736.13911295821</v>
       </c>
       <c r="E72">
-        <v>7969.190000000001</v>
+        <v>8084.277</v>
       </c>
       <c r="F72">
-        <v>8056.09</v>
+        <v>8171.177</v>
       </c>
       <c r="G72">
         <v>119.7</v>
@@ -7179,28 +7179,28 @@
         <v>1191.1</v>
       </c>
       <c r="M72">
-        <v>465.642002</v>
+        <v>472.2940306</v>
       </c>
       <c r="N72">
-        <v>725.4579979999999</v>
+        <v>718.8059693999999</v>
       </c>
       <c r="O72">
-        <v>116.07327968</v>
+        <v>115.008955104</v>
       </c>
       <c r="P72">
-        <v>609.3847183199998</v>
+        <v>603.7970142959999</v>
       </c>
       <c r="Q72">
-        <v>805.2847183199998</v>
+        <v>799.6970142959999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1700974622417469</v>
+        <v>0.1741518995003314</v>
       </c>
       <c r="T72">
-        <v>1.711001353941784</v>
+        <v>1.766812208916587</v>
       </c>
       <c r="U72">
         <v>0.0578</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.557973711314814</v>
+        <v>2.521945912563901</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08497597085509612</v>
+        <v>0.08705310303766813</v>
       </c>
       <c r="C73">
-        <v>3684.66211295821</v>
+        <v>3317.681420377525</v>
       </c>
       <c r="D73">
-        <v>11736.13911295821</v>
+        <v>11484.24542037752</v>
       </c>
       <c r="E73">
-        <v>8084.276999999999</v>
+        <v>8199.364</v>
       </c>
       <c r="F73">
-        <v>8171.176999999999</v>
+        <v>8286.263999999999</v>
       </c>
       <c r="G73">
         <v>119.7</v>
@@ -7261,45 +7261,45 @@
         <v>1191.1</v>
       </c>
       <c r="M73">
-        <v>472.2940306</v>
+        <v>507.9479832</v>
       </c>
       <c r="N73">
-        <v>718.8059693999999</v>
+        <v>683.1520168</v>
       </c>
       <c r="O73">
-        <v>115.008955104</v>
+        <v>109.304322688</v>
       </c>
       <c r="P73">
-        <v>603.7970142959999</v>
+        <v>573.847694112</v>
       </c>
       <c r="Q73">
-        <v>799.6970142959999</v>
+        <v>769.747694112</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1741518995003314</v>
+        <v>0.1784959394202433</v>
       </c>
       <c r="T73">
-        <v>1.766812208916586</v>
+        <v>1.826609553532445</v>
       </c>
       <c r="U73">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V73">
         <v>0.16</v>
       </c>
       <c r="W73">
-        <v>0.048552</v>
+        <v>0.051492</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y73">
-        <v>2.521945912563901</v>
+        <v>2.344925148626912</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08705310303766813</v>
+        <v>0.08704283522024016</v>
       </c>
       <c r="C74">
-        <v>3317.681420377525</v>
+        <v>3203.813001910718</v>
       </c>
       <c r="D74">
-        <v>11484.24542037752</v>
+        <v>11485.46400191072</v>
       </c>
       <c r="E74">
-        <v>8199.364</v>
+        <v>8314.450999999999</v>
       </c>
       <c r="F74">
-        <v>8286.263999999999</v>
+        <v>8401.350999999999</v>
       </c>
       <c r="G74">
         <v>119.7</v>
@@ -7343,28 +7343,28 @@
         <v>1191.1</v>
       </c>
       <c r="M74">
-        <v>507.9479832</v>
+        <v>515.0028162999999</v>
       </c>
       <c r="N74">
-        <v>683.1520168</v>
+        <v>676.0971837</v>
       </c>
       <c r="O74">
-        <v>109.304322688</v>
+        <v>108.175549392</v>
       </c>
       <c r="P74">
-        <v>573.847694112</v>
+        <v>567.921634308</v>
       </c>
       <c r="Q74">
-        <v>769.747694112</v>
+        <v>763.8216343079999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1784959394202433</v>
+        <v>0.1831617600749635</v>
       </c>
       <c r="T74">
-        <v>1.826609553532445</v>
+        <v>1.890836331082812</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.344925148626912</v>
+        <v>2.312802886316954</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08704283522024016</v>
+        <v>0.08703256740281218</v>
       </c>
       <c r="C75">
-        <v>3203.813001910718</v>
+        <v>3089.944842076238</v>
       </c>
       <c r="D75">
-        <v>11485.46400191072</v>
+        <v>11486.68284207624</v>
       </c>
       <c r="E75">
-        <v>8314.450999999999</v>
+        <v>8429.537999999999</v>
       </c>
       <c r="F75">
-        <v>8401.350999999999</v>
+        <v>8516.437999999998</v>
       </c>
       <c r="G75">
         <v>119.7</v>
@@ -7425,28 +7425,28 @@
         <v>1191.1</v>
       </c>
       <c r="M75">
-        <v>515.0028162999999</v>
+        <v>522.0576493999999</v>
       </c>
       <c r="N75">
-        <v>676.0971837</v>
+        <v>669.0423506</v>
       </c>
       <c r="O75">
-        <v>108.175549392</v>
+        <v>107.046776096</v>
       </c>
       <c r="P75">
-        <v>567.921634308</v>
+        <v>561.9955745039999</v>
       </c>
       <c r="Q75">
-        <v>763.8216343079999</v>
+        <v>757.8955745039999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1831617600749635</v>
+        <v>0.1881864900108161</v>
       </c>
       <c r="T75">
-        <v>1.890836331082812</v>
+        <v>1.960003629983208</v>
       </c>
       <c r="U75">
         <v>0.0613</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.312802886316954</v>
+        <v>2.281548793258617</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08703256740281218</v>
+        <v>0.08702229958538421</v>
       </c>
       <c r="C76">
-        <v>3089.944842076238</v>
+        <v>2976.076940956424</v>
       </c>
       <c r="D76">
-        <v>11486.68284207624</v>
+        <v>11487.90194095642</v>
       </c>
       <c r="E76">
-        <v>8429.537999999999</v>
+        <v>8544.625</v>
       </c>
       <c r="F76">
-        <v>8516.437999999998</v>
+        <v>8631.525</v>
       </c>
       <c r="G76">
         <v>119.7</v>
@@ -7507,28 +7507,28 @@
         <v>1191.1</v>
       </c>
       <c r="M76">
-        <v>522.0576493999999</v>
+        <v>529.1124824999999</v>
       </c>
       <c r="N76">
-        <v>669.0423506</v>
+        <v>661.9875175</v>
       </c>
       <c r="O76">
-        <v>107.046776096</v>
+        <v>105.9180028</v>
       </c>
       <c r="P76">
-        <v>561.9955745039999</v>
+        <v>556.0695147</v>
       </c>
       <c r="Q76">
-        <v>757.8955745039999</v>
+        <v>751.9695147</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1881864900108161</v>
+        <v>0.1936131983415369</v>
       </c>
       <c r="T76">
-        <v>1.960003629983208</v>
+        <v>2.034704312795635</v>
       </c>
       <c r="U76">
         <v>0.0613</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.281548793258617</v>
+        <v>2.251128142681835</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08702229958538421</v>
+        <v>0.08879955176795624</v>
       </c>
       <c r="C77">
-        <v>2976.076940956424</v>
+        <v>2653.761082727111</v>
       </c>
       <c r="D77">
-        <v>11487.90194095642</v>
+        <v>11280.67308272711</v>
       </c>
       <c r="E77">
-        <v>8544.625</v>
+        <v>8659.712</v>
       </c>
       <c r="F77">
-        <v>8631.525</v>
+        <v>8746.611999999999</v>
       </c>
       <c r="G77">
         <v>119.7</v>
@@ -7589,45 +7589,45 @@
         <v>1191.1</v>
       </c>
       <c r="M77">
-        <v>529.1124824999999</v>
+        <v>560.6578292</v>
       </c>
       <c r="N77">
-        <v>661.9875175</v>
+        <v>630.4421707999999</v>
       </c>
       <c r="O77">
-        <v>105.9180028</v>
+        <v>100.870747328</v>
       </c>
       <c r="P77">
-        <v>556.0695147</v>
+        <v>529.5714234719999</v>
       </c>
       <c r="Q77">
-        <v>751.9695147</v>
+        <v>725.4714234719999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1936131983415369</v>
+        <v>0.1994921323664844</v>
       </c>
       <c r="T77">
-        <v>2.034704312795635</v>
+        <v>2.115630052509098</v>
       </c>
       <c r="U77">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V77">
         <v>0.16</v>
       </c>
       <c r="W77">
-        <v>0.051492</v>
+        <v>0.053844</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y77">
-        <v>2.251128142681835</v>
+        <v>2.124468682974738</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08879955176795624</v>
+        <v>0.08881280395052828</v>
       </c>
       <c r="C78">
-        <v>2653.761082727111</v>
+        <v>2537.156946880837</v>
       </c>
       <c r="D78">
-        <v>11280.67308272711</v>
+        <v>11279.15594688084</v>
       </c>
       <c r="E78">
-        <v>8659.712</v>
+        <v>8774.798999999999</v>
       </c>
       <c r="F78">
-        <v>8746.611999999999</v>
+        <v>8861.698999999999</v>
       </c>
       <c r="G78">
         <v>119.7</v>
@@ -7671,28 +7671,28 @@
         <v>1191.1</v>
       </c>
       <c r="M78">
-        <v>560.6578292</v>
+        <v>568.0349058999999</v>
       </c>
       <c r="N78">
-        <v>630.4421707999999</v>
+        <v>623.0650941</v>
       </c>
       <c r="O78">
-        <v>100.870747328</v>
+        <v>99.69041505600001</v>
       </c>
       <c r="P78">
-        <v>529.5714234719999</v>
+        <v>523.374679044</v>
       </c>
       <c r="Q78">
-        <v>725.4714234719999</v>
+        <v>719.274679044</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1994921323664844</v>
+        <v>0.2058822780457751</v>
       </c>
       <c r="T78">
-        <v>2.115630052509098</v>
+        <v>2.20359281306721</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.124468682974738</v>
+        <v>2.096878180598444</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08881280395052828</v>
+        <v>0.0888260561331003</v>
       </c>
       <c r="C79">
-        <v>2537.156946880837</v>
+        <v>2420.553219058387</v>
       </c>
       <c r="D79">
-        <v>11279.15594688084</v>
+        <v>11277.63921905839</v>
       </c>
       <c r="E79">
-        <v>8774.798999999999</v>
+        <v>8889.886</v>
       </c>
       <c r="F79">
-        <v>8861.698999999999</v>
+        <v>8976.786</v>
       </c>
       <c r="G79">
         <v>119.7</v>
@@ -7753,28 +7753,28 @@
         <v>1191.1</v>
       </c>
       <c r="M79">
-        <v>568.0349058999999</v>
+        <v>575.4119826</v>
       </c>
       <c r="N79">
-        <v>623.0650941</v>
+        <v>615.6880173999999</v>
       </c>
       <c r="O79">
-        <v>99.69041505600001</v>
+        <v>98.51008278399999</v>
       </c>
       <c r="P79">
-        <v>523.374679044</v>
+        <v>517.1779346159999</v>
       </c>
       <c r="Q79">
-        <v>719.274679044</v>
+        <v>713.0779346159999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2058822780457751</v>
+        <v>0.2128533460595468</v>
       </c>
       <c r="T79">
-        <v>2.20359281306721</v>
+        <v>2.299552188221513</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.096878180598444</v>
+        <v>2.069995127001027</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.0888260561331003</v>
+        <v>0.08883930831567233</v>
       </c>
       <c r="C80">
-        <v>2420.553219058387</v>
+        <v>2303.949899095174</v>
       </c>
       <c r="D80">
-        <v>11277.63921905839</v>
+        <v>11276.12289909517</v>
       </c>
       <c r="E80">
-        <v>8889.886</v>
+        <v>9004.973</v>
       </c>
       <c r="F80">
-        <v>8976.786</v>
+        <v>9091.873</v>
       </c>
       <c r="G80">
         <v>119.7</v>
@@ -7835,28 +7835,28 @@
         <v>1191.1</v>
       </c>
       <c r="M80">
-        <v>575.4119826</v>
+        <v>582.7890593</v>
       </c>
       <c r="N80">
-        <v>615.6880173999999</v>
+        <v>608.3109406999999</v>
       </c>
       <c r="O80">
-        <v>98.51008278399999</v>
+        <v>97.32975051199999</v>
       </c>
       <c r="P80">
-        <v>517.1779346159999</v>
+        <v>510.981190188</v>
       </c>
       <c r="Q80">
-        <v>713.0779346159999</v>
+        <v>706.881190188</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2128533460595468</v>
+        <v>0.2204883253127254</v>
       </c>
       <c r="T80">
-        <v>2.299552188221513</v>
+        <v>2.404650551485751</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.069995127001027</v>
+        <v>2.043792657038989</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08883930831567233</v>
+        <v>0.08885256049824436</v>
       </c>
       <c r="C81">
-        <v>2303.949899095174</v>
+        <v>2187.346986826708</v>
       </c>
       <c r="D81">
-        <v>11276.12289909517</v>
+        <v>11274.60698682671</v>
       </c>
       <c r="E81">
-        <v>9004.973</v>
+        <v>9120.059999999999</v>
       </c>
       <c r="F81">
-        <v>9091.873</v>
+        <v>9206.959999999999</v>
       </c>
       <c r="G81">
         <v>119.7</v>
@@ -7917,28 +7917,28 @@
         <v>1191.1</v>
       </c>
       <c r="M81">
-        <v>582.7890593</v>
+        <v>590.1661359999999</v>
       </c>
       <c r="N81">
-        <v>608.3109406999999</v>
+        <v>600.933864</v>
       </c>
       <c r="O81">
-        <v>97.32975051199999</v>
+        <v>96.14941824</v>
       </c>
       <c r="P81">
-        <v>510.981190188</v>
+        <v>504.78444576</v>
       </c>
       <c r="Q81">
-        <v>706.881190188</v>
+        <v>700.68444576</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2204883253127254</v>
+        <v>0.2288868024912218</v>
       </c>
       <c r="T81">
-        <v>2.404650551485751</v>
+        <v>2.520258751076412</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.043792657038989</v>
+        <v>2.018245248826002</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08885256049824436</v>
+        <v>0.09417293268081639</v>
       </c>
       <c r="C82">
-        <v>2187.346986826708</v>
+        <v>1494.907300295718</v>
       </c>
       <c r="D82">
-        <v>11274.60698682671</v>
+        <v>10697.25430029572</v>
       </c>
       <c r="E82">
-        <v>9120.059999999999</v>
+        <v>9235.147000000001</v>
       </c>
       <c r="F82">
-        <v>9206.959999999999</v>
+        <v>9322.047</v>
       </c>
       <c r="G82">
         <v>119.7</v>
@@ -7999,45 +7999,45 @@
         <v>1191.1</v>
       </c>
       <c r="M82">
-        <v>590.1661359999999</v>
+        <v>670.2551793000001</v>
       </c>
       <c r="N82">
-        <v>600.933864</v>
+        <v>520.8448206999998</v>
       </c>
       <c r="O82">
-        <v>96.14941824</v>
+        <v>83.33517131199997</v>
       </c>
       <c r="P82">
-        <v>504.78444576</v>
+        <v>437.5096493879998</v>
       </c>
       <c r="Q82">
-        <v>700.68444576</v>
+        <v>633.4096493879998</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2288868024912218</v>
+        <v>0.2381693298990337</v>
       </c>
       <c r="T82">
-        <v>2.520258751076412</v>
+        <v>2.648036234834512</v>
       </c>
       <c r="U82">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V82">
         <v>0.16</v>
       </c>
       <c r="W82">
-        <v>0.053844</v>
+        <v>0.06039600000000001</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y82">
-        <v>2.018245248826002</v>
+        <v>1.777084365456092</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09417293268081639</v>
+        <v>0.09425170486338842</v>
       </c>
       <c r="C83">
-        <v>1494.907300295718</v>
+        <v>1371.716031881249</v>
       </c>
       <c r="D83">
-        <v>10697.25430029572</v>
+        <v>10689.15003188125</v>
       </c>
       <c r="E83">
-        <v>9235.147000000001</v>
+        <v>9350.234</v>
       </c>
       <c r="F83">
-        <v>9322.047</v>
+        <v>9437.134</v>
       </c>
       <c r="G83">
         <v>119.7</v>
@@ -8081,28 +8081,28 @@
         <v>1191.1</v>
       </c>
       <c r="M83">
-        <v>670.2551793000001</v>
+        <v>678.5299346</v>
       </c>
       <c r="N83">
-        <v>520.8448206999998</v>
+        <v>512.5700653999999</v>
       </c>
       <c r="O83">
-        <v>83.33517131199997</v>
+        <v>82.01121046399997</v>
       </c>
       <c r="P83">
-        <v>437.5096493879998</v>
+        <v>430.5588549359999</v>
       </c>
       <c r="Q83">
-        <v>633.4096493879998</v>
+        <v>626.4588549359999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2381693298990337</v>
+        <v>0.2484832492410468</v>
       </c>
       <c r="T83">
-        <v>2.648036234834512</v>
+        <v>2.790011216787955</v>
       </c>
       <c r="U83">
         <v>0.07190000000000001</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.777084365456092</v>
+        <v>1.75541260490175</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09425170486338842</v>
+        <v>0.09704955704596044</v>
       </c>
       <c r="C84">
-        <v>1371.716031881249</v>
+        <v>976.534451560532</v>
       </c>
       <c r="D84">
-        <v>10689.15003188125</v>
+        <v>10409.05545156053</v>
       </c>
       <c r="E84">
-        <v>9350.234</v>
+        <v>9465.321</v>
       </c>
       <c r="F84">
-        <v>9437.134</v>
+        <v>9552.221</v>
       </c>
       <c r="G84">
         <v>119.7</v>
@@ -8163,45 +8163,45 @@
         <v>1191.1</v>
       </c>
       <c r="M84">
-        <v>678.5299346</v>
+        <v>724.0583518000001</v>
       </c>
       <c r="N84">
-        <v>512.5700653999999</v>
+        <v>467.0416481999998</v>
       </c>
       <c r="O84">
-        <v>82.01121046399997</v>
+        <v>74.72666371199998</v>
       </c>
       <c r="P84">
-        <v>430.5588549359999</v>
+        <v>392.3149844879998</v>
       </c>
       <c r="Q84">
-        <v>626.4588549359999</v>
+        <v>588.2149844879998</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2484832492410468</v>
+        <v>0.2600105708585909</v>
       </c>
       <c r="T84">
-        <v>2.790011216787955</v>
+        <v>2.948689137794745</v>
       </c>
       <c r="U84">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V84">
         <v>0.16</v>
       </c>
       <c r="W84">
-        <v>0.06039600000000001</v>
+        <v>0.06367200000000001</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y84">
-        <v>1.75541260490175</v>
+        <v>1.645033162091067</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09704955704596044</v>
+        <v>0.09716108922853248</v>
       </c>
       <c r="C85">
-        <v>976.534451560532</v>
+        <v>850.5858247671658</v>
       </c>
       <c r="D85">
-        <v>10409.05545156053</v>
+        <v>10398.19382476717</v>
       </c>
       <c r="E85">
-        <v>9465.321</v>
+        <v>9580.408000000001</v>
       </c>
       <c r="F85">
-        <v>9552.221</v>
+        <v>9667.308000000001</v>
       </c>
       <c r="G85">
         <v>119.7</v>
@@ -8245,28 +8245,28 @@
         <v>1191.1</v>
       </c>
       <c r="M85">
-        <v>724.0583518000001</v>
+        <v>732.7819464000002</v>
       </c>
       <c r="N85">
-        <v>467.0416481999998</v>
+        <v>458.3180535999998</v>
       </c>
       <c r="O85">
-        <v>74.72666371199998</v>
+        <v>73.33088857599996</v>
       </c>
       <c r="P85">
-        <v>392.3149844879998</v>
+        <v>384.9871650239998</v>
       </c>
       <c r="Q85">
-        <v>588.2149844879998</v>
+        <v>580.8871650239998</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2600105708585909</v>
+        <v>0.2729788076783281</v>
       </c>
       <c r="T85">
-        <v>2.948689137794745</v>
+        <v>3.127201798927384</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.645033162091067</v>
+        <v>1.625449433970934</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09716108922853248</v>
+        <v>0.09727262141110449</v>
       </c>
       <c r="C86">
-        <v>850.5858247671677</v>
+        <v>724.6598420957725</v>
       </c>
       <c r="D86">
-        <v>10398.19382476717</v>
+        <v>10387.35484209577</v>
       </c>
       <c r="E86">
-        <v>9580.407999999999</v>
+        <v>9695.494999999999</v>
       </c>
       <c r="F86">
-        <v>9667.307999999999</v>
+        <v>9782.394999999999</v>
       </c>
       <c r="G86">
         <v>119.7</v>
@@ -8327,28 +8327,28 @@
         <v>1191.1</v>
       </c>
       <c r="M86">
-        <v>732.7819464</v>
+        <v>741.505541</v>
       </c>
       <c r="N86">
-        <v>458.3180535999999</v>
+        <v>449.5944589999999</v>
       </c>
       <c r="O86">
-        <v>73.33088857599998</v>
+        <v>71.93511343999999</v>
       </c>
       <c r="P86">
-        <v>384.9871650239999</v>
+        <v>377.6593455599999</v>
       </c>
       <c r="Q86">
-        <v>580.8871650239998</v>
+        <v>573.5593455599999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2729788076783279</v>
+        <v>0.2876761427406966</v>
       </c>
       <c r="T86">
-        <v>3.127201798927382</v>
+        <v>3.329516148211038</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.625449433970935</v>
+        <v>1.60632649945363</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09727262141110449</v>
+        <v>0.09738415359367653</v>
       </c>
       <c r="C87">
-        <v>724.6598420957725</v>
+        <v>598.756432807997</v>
       </c>
       <c r="D87">
-        <v>10387.35484209577</v>
+        <v>10376.53843280799</v>
       </c>
       <c r="E87">
-        <v>9695.494999999999</v>
+        <v>9810.581999999999</v>
       </c>
       <c r="F87">
-        <v>9782.394999999999</v>
+        <v>9897.481999999998</v>
       </c>
       <c r="G87">
         <v>119.7</v>
@@ -8409,28 +8409,28 @@
         <v>1191.1</v>
       </c>
       <c r="M87">
-        <v>741.505541</v>
+        <v>750.2291355999999</v>
       </c>
       <c r="N87">
-        <v>449.5944589999999</v>
+        <v>440.8708644</v>
       </c>
       <c r="O87">
-        <v>71.93511343999999</v>
+        <v>70.539338304</v>
       </c>
       <c r="P87">
-        <v>377.6593455599999</v>
+        <v>370.3315260959999</v>
       </c>
       <c r="Q87">
-        <v>573.5593455599999</v>
+        <v>566.2315260959999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2876761427406966</v>
+        <v>0.3044730970976895</v>
       </c>
       <c r="T87">
-        <v>3.329516148211038</v>
+        <v>3.560732547392361</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.60632649945363</v>
+        <v>1.587648284343704</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09738415359367653</v>
+        <v>0.09749568577624856</v>
       </c>
       <c r="C88">
-        <v>598.756432807997</v>
+        <v>472.8755264598349</v>
       </c>
       <c r="D88">
-        <v>10376.53843280799</v>
+        <v>10365.74452645983</v>
       </c>
       <c r="E88">
-        <v>9810.581999999999</v>
+        <v>9925.669</v>
       </c>
       <c r="F88">
-        <v>9897.481999999998</v>
+        <v>10012.569</v>
       </c>
       <c r="G88">
         <v>119.7</v>
@@ -8491,28 +8491,28 @@
         <v>1191.1</v>
       </c>
       <c r="M88">
-        <v>750.2291355999999</v>
+        <v>758.9527302</v>
       </c>
       <c r="N88">
-        <v>440.8708644</v>
+        <v>432.1472697999999</v>
       </c>
       <c r="O88">
-        <v>70.539338304</v>
+        <v>69.14356316799999</v>
       </c>
       <c r="P88">
-        <v>370.3315260959999</v>
+        <v>363.0037066319999</v>
       </c>
       <c r="Q88">
-        <v>566.2315260959999</v>
+        <v>558.9037066319999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3044730970976895</v>
+        <v>0.323854198278835</v>
       </c>
       <c r="T88">
-        <v>3.560732547392361</v>
+        <v>3.827520700293887</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.587648284343704</v>
+        <v>1.569399453489178</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09749568577624856</v>
+        <v>0.0976072179588206</v>
       </c>
       <c r="C89">
-        <v>472.8755264598349</v>
+        <v>347.0170529000825</v>
       </c>
       <c r="D89">
-        <v>10365.74452645983</v>
+        <v>10354.97305290008</v>
       </c>
       <c r="E89">
-        <v>9925.669</v>
+        <v>10040.756</v>
       </c>
       <c r="F89">
-        <v>10012.569</v>
+        <v>10127.656</v>
       </c>
       <c r="G89">
         <v>119.7</v>
@@ -8573,28 +8573,28 @@
         <v>1191.1</v>
       </c>
       <c r="M89">
-        <v>758.9527302</v>
+        <v>767.6763248</v>
       </c>
       <c r="N89">
-        <v>432.1472697999999</v>
+        <v>423.4236751999999</v>
       </c>
       <c r="O89">
-        <v>69.14356316799999</v>
+        <v>67.74778803199999</v>
       </c>
       <c r="P89">
-        <v>363.0037066319999</v>
+        <v>355.6758871679999</v>
       </c>
       <c r="Q89">
-        <v>558.9037066319999</v>
+        <v>551.5758871679999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.323854198278835</v>
+        <v>0.3464654829901715</v>
       </c>
       <c r="T89">
-        <v>3.827520700293887</v>
+        <v>4.138773545345667</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.569399453489178</v>
+        <v>1.551565368790438</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.0976072179588206</v>
+        <v>0.09771875014139261</v>
       </c>
       <c r="C90">
-        <v>347.0170529000825</v>
+        <v>221.1809422688257</v>
       </c>
       <c r="D90">
-        <v>10354.97305290008</v>
+        <v>10344.22394226882</v>
       </c>
       <c r="E90">
-        <v>10040.756</v>
+        <v>10155.843</v>
       </c>
       <c r="F90">
-        <v>10127.656</v>
+        <v>10242.743</v>
       </c>
       <c r="G90">
         <v>119.7</v>
@@ -8655,28 +8655,28 @@
         <v>1191.1</v>
       </c>
       <c r="M90">
-        <v>767.6763248</v>
+        <v>776.3999193999999</v>
       </c>
       <c r="N90">
-        <v>423.4236751999999</v>
+        <v>414.7000806</v>
       </c>
       <c r="O90">
-        <v>67.74778803199999</v>
+        <v>66.35201289599999</v>
       </c>
       <c r="P90">
-        <v>355.6758871679999</v>
+        <v>348.348067704</v>
       </c>
       <c r="Q90">
-        <v>551.5758871679999</v>
+        <v>544.2480677039999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3464654829901715</v>
+        <v>0.3731879103762965</v>
       </c>
       <c r="T90">
-        <v>4.138773545345667</v>
+        <v>4.506617816770498</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.551565368790438</v>
+        <v>1.534132050039984</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09771875014139261</v>
+        <v>0.09783028232396465</v>
       </c>
       <c r="C91">
-        <v>221.1809422688257</v>
+        <v>95.36712499591158</v>
       </c>
       <c r="D91">
-        <v>10344.22394226882</v>
+        <v>10333.49712499591</v>
       </c>
       <c r="E91">
-        <v>10155.843</v>
+        <v>10270.93</v>
       </c>
       <c r="F91">
-        <v>10242.743</v>
+        <v>10357.83</v>
       </c>
       <c r="G91">
         <v>119.7</v>
@@ -8737,28 +8737,28 @@
         <v>1191.1</v>
       </c>
       <c r="M91">
-        <v>776.3999193999999</v>
+        <v>785.1235140000001</v>
       </c>
       <c r="N91">
-        <v>414.7000806</v>
+        <v>405.9764859999998</v>
       </c>
       <c r="O91">
-        <v>66.35201289599999</v>
+        <v>64.95623775999996</v>
       </c>
       <c r="P91">
-        <v>348.348067704</v>
+        <v>341.0202482399998</v>
       </c>
       <c r="Q91">
-        <v>544.2480677039999</v>
+        <v>536.9202482399999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3731879103762965</v>
+        <v>0.4052548232396466</v>
       </c>
       <c r="T91">
-        <v>4.506617816770498</v>
+        <v>4.948030942480296</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.534132050039984</v>
+        <v>1.517086138372872</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09783028232396465</v>
+        <v>0.09794181450653669</v>
       </c>
       <c r="C92">
-        <v>95.36712499591158</v>
+        <v>-30.42446820052282</v>
       </c>
       <c r="D92">
-        <v>10333.49712499591</v>
+        <v>10322.79253179948</v>
       </c>
       <c r="E92">
-        <v>10270.93</v>
+        <v>10386.017</v>
       </c>
       <c r="F92">
-        <v>10357.83</v>
+        <v>10472.917</v>
       </c>
       <c r="G92">
         <v>119.7</v>
@@ -8819,28 +8819,28 @@
         <v>1191.1</v>
       </c>
       <c r="M92">
-        <v>785.1235140000001</v>
+        <v>793.8471086000001</v>
       </c>
       <c r="N92">
-        <v>405.9764859999998</v>
+        <v>397.2528913999998</v>
       </c>
       <c r="O92">
-        <v>64.95623775999996</v>
+        <v>63.56046262399997</v>
       </c>
       <c r="P92">
-        <v>341.0202482399998</v>
+        <v>333.6924287759999</v>
       </c>
       <c r="Q92">
-        <v>536.9202482399999</v>
+        <v>529.5924287759999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4052548232396466</v>
+        <v>0.4444477167392965</v>
       </c>
       <c r="T92">
-        <v>4.948030942480296</v>
+        <v>5.487535873903381</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.517086138372872</v>
+        <v>1.500414862127017</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09794181450653669</v>
+        <v>0.1323459805493012</v>
       </c>
       <c r="C93">
-        <v>-30.42446820052282</v>
+        <v>-2645.31727218542</v>
       </c>
       <c r="D93">
-        <v>10322.79253179948</v>
+        <v>7822.986727814579</v>
       </c>
       <c r="E93">
-        <v>10386.017</v>
+        <v>10501.104</v>
       </c>
       <c r="F93">
-        <v>10472.917</v>
+        <v>10588.004</v>
       </c>
       <c r="G93">
         <v>119.7</v>
@@ -8901,45 +8901,45 @@
         <v>1191.1</v>
       </c>
       <c r="M93">
-        <v>793.8471086000001</v>
+        <v>1255.7372744</v>
       </c>
       <c r="N93">
-        <v>397.2528913999998</v>
+        <v>-64.63727440000002</v>
       </c>
       <c r="O93">
-        <v>63.56046262399997</v>
+        <v>-10.341963904</v>
       </c>
       <c r="P93">
-        <v>333.6924287759999</v>
+        <v>-54.29531049600002</v>
       </c>
       <c r="Q93">
-        <v>529.5924287759999</v>
+        <v>141.604689504</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4444477167392965</v>
+        <v>0.4974159895858592</v>
       </c>
       <c r="T93">
-        <v>5.487535873903381</v>
+        <v>6.216664087158147</v>
       </c>
       <c r="U93">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V93">
-        <v>0.16</v>
+        <v>0.1517642295766513</v>
       </c>
       <c r="W93">
-        <v>0.06367200000000001</v>
+        <v>0.1006007623722092</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y93">
-        <v>1.500414862127017</v>
+        <v>0.9485264348540707</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1323459805493012</v>
+        <v>0.1330739805493011</v>
       </c>
       <c r="C94">
-        <v>-2645.31727218542</v>
+        <v>-2800.286762127256</v>
       </c>
       <c r="D94">
-        <v>7822.986727814579</v>
+        <v>7783.104237872744</v>
       </c>
       <c r="E94">
-        <v>10501.104</v>
+        <v>10616.191</v>
       </c>
       <c r="F94">
-        <v>10588.004</v>
+        <v>10703.091</v>
       </c>
       <c r="G94">
         <v>119.7</v>
@@ -8983,37 +8983,37 @@
         <v>1191.1</v>
       </c>
       <c r="M94">
-        <v>1255.7372744</v>
+        <v>1269.3865926</v>
       </c>
       <c r="N94">
-        <v>-64.63727440000002</v>
+        <v>-78.28659260000018</v>
       </c>
       <c r="O94">
-        <v>-10.341963904</v>
+        <v>-12.52585481600003</v>
       </c>
       <c r="P94">
-        <v>-54.29531049600002</v>
+        <v>-65.76073778400014</v>
       </c>
       <c r="Q94">
-        <v>141.604689504</v>
+        <v>130.1392622159998</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4974159895858592</v>
+        <v>0.5619325595266962</v>
       </c>
       <c r="T94">
-        <v>6.216664087158147</v>
+        <v>7.104758956752169</v>
       </c>
       <c r="U94">
         <v>0.1186</v>
       </c>
       <c r="V94">
-        <v>0.1517642295766513</v>
+        <v>0.1501323561403432</v>
       </c>
       <c r="W94">
-        <v>0.1006007623722092</v>
+        <v>0.1007943025617553</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.9485264348540707</v>
+        <v>0.9383272258771451</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1330739805493011</v>
+        <v>0.1338019805493012</v>
       </c>
       <c r="C95">
-        <v>-2800.286762127256</v>
+        <v>-2954.851663626905</v>
       </c>
       <c r="D95">
-        <v>7783.104237872744</v>
+        <v>7743.626336373095</v>
       </c>
       <c r="E95">
-        <v>10616.191</v>
+        <v>10731.278</v>
       </c>
       <c r="F95">
-        <v>10703.091</v>
+        <v>10818.178</v>
       </c>
       <c r="G95">
         <v>119.7</v>
@@ -9065,37 +9065,37 @@
         <v>1191.1</v>
       </c>
       <c r="M95">
-        <v>1269.3865926</v>
+        <v>1283.0359108</v>
       </c>
       <c r="N95">
-        <v>-78.28659260000018</v>
+        <v>-91.9359108000001</v>
       </c>
       <c r="O95">
-        <v>-12.52585481600003</v>
+        <v>-14.70974572800002</v>
       </c>
       <c r="P95">
-        <v>-65.76073778400014</v>
+        <v>-77.22616507200009</v>
       </c>
       <c r="Q95">
-        <v>130.1392622159998</v>
+        <v>118.6738349279999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5619325595266962</v>
+        <v>0.6479546527811459</v>
       </c>
       <c r="T95">
-        <v>7.104758956752169</v>
+        <v>8.288885449544201</v>
       </c>
       <c r="U95">
         <v>0.1186</v>
       </c>
       <c r="V95">
-        <v>0.1501323561403432</v>
+        <v>0.148535203415446</v>
       </c>
       <c r="W95">
-        <v>0.1007943025617553</v>
+        <v>0.1009837248749281</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.9383272258771451</v>
+        <v>0.9283450213465373</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1338019805493012</v>
+        <v>0.1345299805493012</v>
       </c>
       <c r="C96">
-        <v>-2954.851663626905</v>
+        <v>-3109.018102143602</v>
       </c>
       <c r="D96">
-        <v>7743.626336373095</v>
+        <v>7704.546897856398</v>
       </c>
       <c r="E96">
-        <v>10731.278</v>
+        <v>10846.365</v>
       </c>
       <c r="F96">
-        <v>10818.178</v>
+        <v>10933.265</v>
       </c>
       <c r="G96">
         <v>119.7</v>
@@ -9147,37 +9147,37 @@
         <v>1191.1</v>
       </c>
       <c r="M96">
-        <v>1283.0359108</v>
+        <v>1296.685229</v>
       </c>
       <c r="N96">
-        <v>-91.9359108000001</v>
+        <v>-105.5852290000003</v>
       </c>
       <c r="O96">
-        <v>-14.70974572800002</v>
+        <v>-16.89363664000004</v>
       </c>
       <c r="P96">
-        <v>-77.22616507200009</v>
+        <v>-88.69159236000021</v>
       </c>
       <c r="Q96">
-        <v>118.6738349279999</v>
+        <v>107.2084076399998</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6479546527811459</v>
+        <v>0.7683855833373753</v>
       </c>
       <c r="T96">
-        <v>8.288885449544201</v>
+        <v>9.946662539453044</v>
       </c>
       <c r="U96">
         <v>0.1186</v>
       </c>
       <c r="V96">
-        <v>0.148535203415446</v>
+        <v>0.1469716749584413</v>
       </c>
       <c r="W96">
-        <v>0.1009837248749281</v>
+        <v>0.1011691593499289</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.9283450213465373</v>
+        <v>0.9185729684902578</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1345299805493012</v>
+        <v>0.1352579805493012</v>
       </c>
       <c r="C97">
-        <v>-3109.018102143602</v>
+        <v>-3262.792080105076</v>
       </c>
       <c r="D97">
-        <v>7704.546897856398</v>
+        <v>7665.859919894923</v>
       </c>
       <c r="E97">
-        <v>10846.365</v>
+        <v>10961.452</v>
       </c>
       <c r="F97">
-        <v>10933.265</v>
+        <v>11048.352</v>
       </c>
       <c r="G97">
         <v>119.7</v>
@@ -9229,37 +9229,37 @@
         <v>1191.1</v>
       </c>
       <c r="M97">
-        <v>1296.685229</v>
+        <v>1310.3345472</v>
       </c>
       <c r="N97">
-        <v>-105.5852290000003</v>
+        <v>-119.2345472000002</v>
       </c>
       <c r="O97">
-        <v>-16.89363664000004</v>
+        <v>-19.07752755200003</v>
       </c>
       <c r="P97">
-        <v>-88.69159236000021</v>
+        <v>-100.1570196480002</v>
       </c>
       <c r="Q97">
-        <v>107.2084076399998</v>
+        <v>95.74298035199985</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7683855833373753</v>
+        <v>0.9490319791717197</v>
       </c>
       <c r="T97">
-        <v>9.946662539453044</v>
+        <v>12.43332817431631</v>
       </c>
       <c r="U97">
         <v>0.1186</v>
       </c>
       <c r="V97">
-        <v>0.1469716749584413</v>
+        <v>0.1454407200109575</v>
       </c>
       <c r="W97">
-        <v>0.1011691593499289</v>
+        <v>0.1013507306067004</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.9185729684902578</v>
+        <v>0.9090045000684843</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1352579805493011</v>
+        <v>0.1359859805493012</v>
       </c>
       <c r="C98">
-        <v>-3262.792080105073</v>
+        <v>-3416.17947998101</v>
       </c>
       <c r="D98">
-        <v>7665.859919894926</v>
+        <v>7627.559520018988</v>
       </c>
       <c r="E98">
-        <v>10961.452</v>
+        <v>11076.539</v>
       </c>
       <c r="F98">
-        <v>11048.352</v>
+        <v>11163.439</v>
       </c>
       <c r="G98">
         <v>119.7</v>
@@ -9311,37 +9311,37 @@
         <v>1191.1</v>
       </c>
       <c r="M98">
-        <v>1310.3345472</v>
+        <v>1323.9838654</v>
       </c>
       <c r="N98">
-        <v>-119.2345472000002</v>
+        <v>-132.8838654000001</v>
       </c>
       <c r="O98">
-        <v>-19.07752755200003</v>
+        <v>-21.26141846400002</v>
       </c>
       <c r="P98">
-        <v>-100.1570196480002</v>
+        <v>-111.6224469360001</v>
       </c>
       <c r="Q98">
-        <v>95.74298035199985</v>
+        <v>84.27755306399992</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9490319791717171</v>
+        <v>1.25010930556229</v>
       </c>
       <c r="T98">
-        <v>12.43332817431628</v>
+        <v>16.57777089908837</v>
       </c>
       <c r="U98">
         <v>0.1186</v>
       </c>
       <c r="V98">
-        <v>0.1454407200109575</v>
+        <v>0.1439413311448652</v>
       </c>
       <c r="W98">
-        <v>0.1013507306067004</v>
+        <v>0.101528558126219</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.9090045000684843</v>
+        <v>0.8996333196554073</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1359859805493012</v>
+        <v>0.1367139805493011</v>
       </c>
       <c r="C99">
-        <v>-3416.17947998101</v>
+        <v>-3569.186067264847</v>
       </c>
       <c r="D99">
-        <v>7627.559520018988</v>
+        <v>7589.639932735151</v>
       </c>
       <c r="E99">
-        <v>11076.539</v>
+        <v>11191.626</v>
       </c>
       <c r="F99">
-        <v>11163.439</v>
+        <v>11278.526</v>
       </c>
       <c r="G99">
         <v>119.7</v>
@@ -9393,37 +9393,37 @@
         <v>1191.1</v>
       </c>
       <c r="M99">
-        <v>1323.9838654</v>
+        <v>1337.6331836</v>
       </c>
       <c r="N99">
-        <v>-132.8838654000001</v>
+        <v>-146.5331836</v>
       </c>
       <c r="O99">
-        <v>-21.26141846400002</v>
+        <v>-23.445309376</v>
       </c>
       <c r="P99">
-        <v>-111.6224469360001</v>
+        <v>-123.087874224</v>
       </c>
       <c r="Q99">
-        <v>84.27755306399992</v>
+        <v>72.81212577599999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.25010930556229</v>
+        <v>1.852263958343434</v>
       </c>
       <c r="T99">
-        <v>16.57777089908837</v>
+        <v>24.86665634863255</v>
       </c>
       <c r="U99">
         <v>0.1186</v>
       </c>
       <c r="V99">
-        <v>0.1439413311448652</v>
+        <v>0.1424725420515502</v>
       </c>
       <c r="W99">
-        <v>0.101528558126219</v>
+        <v>0.1017027565126861</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8996333196554073</v>
+        <v>0.8904533878221889</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1367139805493011</v>
+        <v>0.1374419805493012</v>
       </c>
       <c r="C100">
-        <v>-3569.186067264847</v>
+        <v>-3721.81749336707</v>
       </c>
       <c r="D100">
-        <v>7589.639932735151</v>
+        <v>7552.09550663293</v>
       </c>
       <c r="E100">
-        <v>11191.626</v>
+        <v>11306.713</v>
       </c>
       <c r="F100">
-        <v>11278.526</v>
+        <v>11393.613</v>
       </c>
       <c r="G100">
         <v>119.7</v>
@@ -9475,37 +9475,37 @@
         <v>1191.1</v>
       </c>
       <c r="M100">
-        <v>1337.6331836</v>
+        <v>1351.2825018</v>
       </c>
       <c r="N100">
-        <v>-146.5331836</v>
+        <v>-160.1825018000002</v>
       </c>
       <c r="O100">
-        <v>-23.445309376</v>
+        <v>-25.62920028800003</v>
       </c>
       <c r="P100">
-        <v>-123.087874224</v>
+        <v>-134.5533015120002</v>
       </c>
       <c r="Q100">
-        <v>72.81212577599999</v>
+        <v>61.34669848799984</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.852263958343434</v>
+        <v>3.658727916686868</v>
       </c>
       <c r="T100">
-        <v>24.86665634863255</v>
+        <v>49.73331269726511</v>
       </c>
       <c r="U100">
         <v>0.1186</v>
       </c>
       <c r="V100">
-        <v>0.1424725420515502</v>
+        <v>0.1410334254651709</v>
       </c>
       <c r="W100">
-        <v>0.1017027565126861</v>
+        <v>0.1018734357398307</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8904533878221889</v>
+        <v>0.8814589091573182</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1374419805493012</v>
-      </c>
-      <c r="C101">
-        <v>-3721.81749336707</v>
-      </c>
-      <c r="D101">
-        <v>7552.09550663293</v>
-      </c>
-      <c r="E101">
-        <v>11306.713</v>
-      </c>
-      <c r="F101">
-        <v>11393.613</v>
-      </c>
-      <c r="G101">
-        <v>119.7</v>
-      </c>
-      <c r="H101">
-        <v>11421.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1387</v>
-      </c>
-      <c r="K101">
-        <v>195.9</v>
-      </c>
-      <c r="L101">
-        <v>1191.1</v>
-      </c>
-      <c r="M101">
-        <v>1351.2825018</v>
-      </c>
-      <c r="N101">
-        <v>-160.1825018000002</v>
-      </c>
-      <c r="O101">
-        <v>-25.62920028800003</v>
-      </c>
-      <c r="P101">
-        <v>-134.5533015120002</v>
-      </c>
-      <c r="Q101">
-        <v>61.34669848799984</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.658727916686868</v>
-      </c>
-      <c r="T101">
-        <v>49.73331269726511</v>
-      </c>
-      <c r="U101">
-        <v>0.1186</v>
-      </c>
-      <c r="V101">
-        <v>0.1410334254651709</v>
-      </c>
-      <c r="W101">
-        <v>0.1018734357398307</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Caa/CCC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8814589091573182</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
